--- a/output/final_classification.xlsx
+++ b/output/final_classification.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2308" uniqueCount="1048">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2378" uniqueCount="1077">
   <si>
     <t>transaction_id</t>
   </si>
@@ -1330,6 +1330,12 @@
     <t>Marketing Technology</t>
   </si>
   <si>
+    <t>Events &amp; Sponsorship</t>
+  </si>
+  <si>
+    <t>Print &amp; Managed Print</t>
+  </si>
+  <si>
     <t>Insurance</t>
   </si>
   <si>
@@ -1378,9 +1384,6 @@
     <t>Office Supplies</t>
   </si>
   <si>
-    <t>Print &amp; Managed Print</t>
-  </si>
-  <si>
     <t>Productivity &amp; Collaboration</t>
   </si>
   <si>
@@ -1579,6 +1582,18 @@
     <t>Out-of-Home</t>
   </si>
   <si>
+    <t>Events</t>
+  </si>
+  <si>
+    <t>Email &amp; CRM</t>
+  </si>
+  <si>
+    <t>Sponsorship</t>
+  </si>
+  <si>
+    <t>Print Production</t>
+  </si>
+  <si>
     <t>Financial Lines</t>
   </si>
   <si>
@@ -1696,9 +1711,6 @@
     <t>Office Equipment</t>
   </si>
   <si>
-    <t>Print Production</t>
-  </si>
-  <si>
     <t>Catering &amp; Hospitality</t>
   </si>
   <si>
@@ -1960,6 +1972,30 @@
     <t>Billboard &amp; Poster Advertising</t>
   </si>
   <si>
+    <t>Conference &amp; Event Management</t>
+  </si>
+  <si>
+    <t>Loyalty &amp; Rewards Technology</t>
+  </si>
+  <si>
+    <t>Brand Strategy &amp; Design</t>
+  </si>
+  <si>
+    <t>Digital OOH</t>
+  </si>
+  <si>
+    <t>Email Marketing Platforms</t>
+  </si>
+  <si>
+    <t>Sports &amp; Entertainment Sponsorship</t>
+  </si>
+  <si>
+    <t>Social Media Management</t>
+  </si>
+  <si>
+    <t>External Print Production</t>
+  </si>
+  <si>
     <t>Regulatory Compliance Advisory</t>
   </si>
   <si>
@@ -2470,6 +2506,36 @@
     <t>OOH poster sites correspond to Billboard &amp; Poster Advertising.</t>
   </si>
   <si>
+    <t>The spend is for a client conference with 600 delegates, which directly matches the Conference &amp; Event Management category under Events &amp; Sponsorship.</t>
+  </si>
+  <si>
+    <t>The purchase is a SaaS loyalty platform for the Boots Advantage Card, fitting the Loyalty &amp; Rewards Technology sub‑category of MarTech Platforms.</t>
+  </si>
+  <si>
+    <t>The engagement is a global brand identity refresh and brand guidelines, which aligns with Brand Strategy &amp; Design under Brand &amp; Identity.</t>
+  </si>
+  <si>
+    <t>The employer brand campaign includes digital out‑of‑home advertising, matching the Digital OOH category under Out‑of‑Home advertising.</t>
+  </si>
+  <si>
+    <t>Shopper marketing and in‑store activation are typically delivered via marketing cloud platforms; this is the most specific MarTech option available.</t>
+  </si>
+  <si>
+    <t>Klaviyo provides an email marketing SaaS platform, directly matching the Email Marketing Platforms leaf node.</t>
+  </si>
+  <si>
+    <t>A brand tracking study is a research service supporting brand strategy, best fitting the Brand Strategy &amp; Design category among the provided options.</t>
+  </si>
+  <si>
+    <t>Shirt sponsorship rights for the Premier League are a sports sponsorship, aligning with Sports &amp; Entertainment Sponsorship.</t>
+  </si>
+  <si>
+    <t>Hootsuite Enterprise is a social media management SaaS platform, fitting the Social Media Management leaf node.</t>
+  </si>
+  <si>
+    <t>The spend covers design and external printing of patient information leaflets, matching External Print Production under Print Production.</t>
+  </si>
+  <si>
     <t>The retainer provides regulatory compliance advisory for FCA financial promotions, matching the Regulatory Compliance Advisory commodity.</t>
   </si>
   <si>
@@ -2713,9 +2779,6 @@
     <t>REVIEW</t>
   </si>
   <si>
-    <t>INVALID</t>
-  </si>
-  <si>
     <t>ACCEPTED</t>
   </si>
   <si>
@@ -2978,6 +3041,30 @@
   </si>
   <si>
     <t>Marketing &amp; Communications &gt; Advertising &gt; Out-of-Home &gt; Billboard &amp; Poster Advertising</t>
+  </si>
+  <si>
+    <t>Marketing &amp; Communications &gt; Events &amp; Sponsorship &gt; Events &gt; Conference &amp; Event Management</t>
+  </si>
+  <si>
+    <t>Marketing &amp; Communications &gt; Marketing Technology &gt; MarTech Platforms &gt; Loyalty &amp; Rewards Technology</t>
+  </si>
+  <si>
+    <t>Marketing &amp; Communications &gt; Creative &amp; Design &gt; Brand &amp; Identity &gt; Brand Strategy &amp; Design</t>
+  </si>
+  <si>
+    <t>Marketing &amp; Communications &gt; Advertising &gt; Out-of-Home &gt; Digital OOH</t>
+  </si>
+  <si>
+    <t>Marketing &amp; Communications &gt; Digital Marketing &gt; Email &amp; CRM &gt; Email Marketing Platforms</t>
+  </si>
+  <si>
+    <t>Marketing &amp; Communications &gt; Events &amp; Sponsorship &gt; Sponsorship &gt; Sports &amp; Entertainment Sponsorship</t>
+  </si>
+  <si>
+    <t>Marketing &amp; Communications &gt; Digital Marketing &gt; Influencer &amp; Social &gt; Social Media Management</t>
+  </si>
+  <si>
+    <t>Print, Office &amp; Corporate &gt; Print &amp; Managed Print &gt; Print Production &gt; External Print Production</t>
   </si>
   <si>
     <t>Professional Services &gt; Legal Services &gt; Regulatory &amp; Compliance &gt; Regulatory Compliance Advisory</t>
@@ -3556,28 +3643,28 @@
         <v>407</v>
       </c>
       <c r="G2" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="H2" t="s">
-        <v>562</v>
+        <v>566</v>
       </c>
       <c r="I2" t="s">
-        <v>708</v>
+        <v>720</v>
       </c>
       <c r="J2" t="s">
-        <v>894</v>
+        <v>916</v>
       </c>
       <c r="K2" t="s">
-        <v>897</v>
+        <v>919</v>
       </c>
       <c r="L2" t="b">
         <v>0</v>
       </c>
       <c r="M2" t="s">
-        <v>900</v>
+        <v>921</v>
       </c>
       <c r="N2" t="s">
-        <v>902</v>
+        <v>923</v>
       </c>
     </row>
     <row r="3" spans="1:14">
@@ -3600,28 +3687,28 @@
         <v>407</v>
       </c>
       <c r="G3" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="H3" t="s">
-        <v>562</v>
+        <v>566</v>
       </c>
       <c r="I3" t="s">
-        <v>708</v>
+        <v>720</v>
       </c>
       <c r="J3" t="s">
-        <v>894</v>
+        <v>916</v>
       </c>
       <c r="K3" t="s">
-        <v>897</v>
+        <v>919</v>
       </c>
       <c r="L3" t="b">
         <v>0</v>
       </c>
       <c r="M3" t="s">
-        <v>900</v>
+        <v>921</v>
       </c>
       <c r="N3" t="s">
-        <v>902</v>
+        <v>923</v>
       </c>
     </row>
     <row r="4" spans="1:14">
@@ -3644,28 +3731,28 @@
         <v>408</v>
       </c>
       <c r="G4" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="H4" t="s">
-        <v>563</v>
+        <v>567</v>
       </c>
       <c r="I4" t="s">
-        <v>709</v>
+        <v>721</v>
       </c>
       <c r="J4" t="s">
-        <v>894</v>
+        <v>916</v>
       </c>
       <c r="K4" t="s">
-        <v>897</v>
+        <v>919</v>
       </c>
       <c r="L4" t="b">
         <v>0</v>
       </c>
       <c r="M4" t="s">
-        <v>900</v>
+        <v>921</v>
       </c>
       <c r="N4" t="s">
-        <v>903</v>
+        <v>924</v>
       </c>
     </row>
     <row r="5" spans="1:14">
@@ -3688,28 +3775,28 @@
         <v>407</v>
       </c>
       <c r="G5" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="H5" t="s">
-        <v>564</v>
+        <v>568</v>
       </c>
       <c r="I5" t="s">
-        <v>710</v>
+        <v>722</v>
       </c>
       <c r="J5" t="s">
-        <v>894</v>
+        <v>916</v>
       </c>
       <c r="K5" t="s">
-        <v>897</v>
+        <v>919</v>
       </c>
       <c r="L5" t="b">
         <v>0</v>
       </c>
       <c r="M5" t="s">
-        <v>900</v>
+        <v>921</v>
       </c>
       <c r="N5" t="s">
-        <v>904</v>
+        <v>925</v>
       </c>
     </row>
     <row r="6" spans="1:14">
@@ -3732,28 +3819,28 @@
         <v>407</v>
       </c>
       <c r="G6" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="H6" t="s">
-        <v>565</v>
+        <v>569</v>
       </c>
       <c r="I6" t="s">
-        <v>711</v>
+        <v>723</v>
       </c>
       <c r="J6" t="s">
-        <v>894</v>
+        <v>916</v>
       </c>
       <c r="K6" t="s">
-        <v>897</v>
+        <v>919</v>
       </c>
       <c r="L6" t="b">
         <v>0</v>
       </c>
       <c r="M6" t="s">
-        <v>900</v>
+        <v>921</v>
       </c>
       <c r="N6" t="s">
-        <v>905</v>
+        <v>926</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -3776,28 +3863,28 @@
         <v>407</v>
       </c>
       <c r="G7" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="H7" t="s">
-        <v>566</v>
+        <v>570</v>
       </c>
       <c r="I7" t="s">
-        <v>712</v>
+        <v>724</v>
       </c>
       <c r="J7" t="s">
-        <v>894</v>
+        <v>916</v>
       </c>
       <c r="K7" t="s">
-        <v>897</v>
+        <v>919</v>
       </c>
       <c r="L7" t="b">
         <v>0</v>
       </c>
       <c r="M7" t="s">
-        <v>900</v>
+        <v>921</v>
       </c>
       <c r="N7" t="s">
-        <v>906</v>
+        <v>927</v>
       </c>
     </row>
     <row r="8" spans="1:14">
@@ -3820,28 +3907,28 @@
         <v>409</v>
       </c>
       <c r="G8" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H8" t="s">
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="I8" t="s">
-        <v>713</v>
+        <v>725</v>
       </c>
       <c r="J8" t="s">
-        <v>894</v>
+        <v>916</v>
       </c>
       <c r="K8" t="s">
-        <v>897</v>
+        <v>919</v>
       </c>
       <c r="L8" t="b">
         <v>0</v>
       </c>
       <c r="M8" t="s">
-        <v>900</v>
+        <v>921</v>
       </c>
       <c r="N8" t="s">
-        <v>907</v>
+        <v>928</v>
       </c>
     </row>
     <row r="9" spans="1:14">
@@ -3864,28 +3951,28 @@
         <v>410</v>
       </c>
       <c r="G9" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="H9" t="s">
-        <v>568</v>
+        <v>572</v>
       </c>
       <c r="I9" t="s">
-        <v>714</v>
+        <v>726</v>
       </c>
       <c r="J9" t="s">
-        <v>895</v>
+        <v>917</v>
       </c>
       <c r="K9" t="s">
-        <v>897</v>
+        <v>919</v>
       </c>
       <c r="L9" t="b">
         <v>1</v>
       </c>
       <c r="M9" t="s">
-        <v>901</v>
+        <v>922</v>
       </c>
       <c r="N9" t="s">
-        <v>908</v>
+        <v>929</v>
       </c>
     </row>
     <row r="10" spans="1:14">
@@ -3908,28 +3995,28 @@
         <v>410</v>
       </c>
       <c r="G10" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="H10" t="s">
-        <v>569</v>
+        <v>573</v>
       </c>
       <c r="I10" t="s">
-        <v>715</v>
+        <v>727</v>
       </c>
       <c r="J10" t="s">
-        <v>894</v>
+        <v>916</v>
       </c>
       <c r="K10" t="s">
-        <v>897</v>
+        <v>919</v>
       </c>
       <c r="L10" t="b">
         <v>0</v>
       </c>
       <c r="M10" t="s">
-        <v>900</v>
+        <v>921</v>
       </c>
       <c r="N10" t="s">
-        <v>909</v>
+        <v>930</v>
       </c>
     </row>
     <row r="11" spans="1:14">
@@ -3952,28 +4039,28 @@
         <v>407</v>
       </c>
       <c r="G11" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="H11" t="s">
-        <v>570</v>
+        <v>574</v>
       </c>
       <c r="I11" t="s">
-        <v>716</v>
+        <v>728</v>
       </c>
       <c r="J11" t="s">
-        <v>894</v>
+        <v>916</v>
       </c>
       <c r="K11" t="s">
-        <v>897</v>
+        <v>919</v>
       </c>
       <c r="L11" t="b">
         <v>0</v>
       </c>
       <c r="M11" t="s">
-        <v>900</v>
+        <v>921</v>
       </c>
       <c r="N11" t="s">
-        <v>910</v>
+        <v>931</v>
       </c>
     </row>
     <row r="12" spans="1:14">
@@ -3996,28 +4083,28 @@
         <v>408</v>
       </c>
       <c r="G12" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="H12" t="s">
-        <v>563</v>
+        <v>567</v>
       </c>
       <c r="I12" t="s">
-        <v>717</v>
+        <v>729</v>
       </c>
       <c r="J12" t="s">
-        <v>895</v>
+        <v>917</v>
       </c>
       <c r="K12" t="s">
-        <v>897</v>
+        <v>919</v>
       </c>
       <c r="L12" t="b">
         <v>1</v>
       </c>
       <c r="M12" t="s">
-        <v>901</v>
+        <v>922</v>
       </c>
       <c r="N12" t="s">
-        <v>903</v>
+        <v>924</v>
       </c>
     </row>
     <row r="13" spans="1:14">
@@ -4040,28 +4127,28 @@
         <v>411</v>
       </c>
       <c r="G13" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="H13" t="s">
-        <v>571</v>
+        <v>575</v>
       </c>
       <c r="I13" t="s">
-        <v>718</v>
+        <v>730</v>
       </c>
       <c r="J13" t="s">
-        <v>894</v>
+        <v>916</v>
       </c>
       <c r="K13" t="s">
-        <v>897</v>
+        <v>919</v>
       </c>
       <c r="L13" t="b">
         <v>0</v>
       </c>
       <c r="M13" t="s">
-        <v>900</v>
+        <v>921</v>
       </c>
       <c r="N13" t="s">
-        <v>911</v>
+        <v>932</v>
       </c>
     </row>
     <row r="14" spans="1:14">
@@ -4084,28 +4171,28 @@
         <v>412</v>
       </c>
       <c r="G14" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="H14" t="s">
-        <v>572</v>
+        <v>576</v>
       </c>
       <c r="I14" t="s">
-        <v>719</v>
+        <v>731</v>
       </c>
       <c r="J14" t="s">
-        <v>894</v>
+        <v>916</v>
       </c>
       <c r="K14" t="s">
-        <v>897</v>
+        <v>919</v>
       </c>
       <c r="L14" t="b">
         <v>0</v>
       </c>
       <c r="M14" t="s">
-        <v>900</v>
+        <v>921</v>
       </c>
       <c r="N14" t="s">
-        <v>912</v>
+        <v>933</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -4128,28 +4215,28 @@
         <v>407</v>
       </c>
       <c r="G15" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="H15" t="s">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="I15" t="s">
-        <v>720</v>
+        <v>732</v>
       </c>
       <c r="J15" t="s">
-        <v>894</v>
+        <v>916</v>
       </c>
       <c r="K15" t="s">
-        <v>897</v>
+        <v>919</v>
       </c>
       <c r="L15" t="b">
         <v>0</v>
       </c>
       <c r="M15" t="s">
-        <v>900</v>
+        <v>921</v>
       </c>
       <c r="N15" t="s">
-        <v>913</v>
+        <v>934</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -4172,28 +4259,28 @@
         <v>409</v>
       </c>
       <c r="G16" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H16" t="s">
-        <v>574</v>
+        <v>578</v>
       </c>
       <c r="I16" t="s">
-        <v>721</v>
+        <v>733</v>
       </c>
       <c r="J16" t="s">
-        <v>894</v>
+        <v>916</v>
       </c>
       <c r="K16" t="s">
-        <v>897</v>
+        <v>919</v>
       </c>
       <c r="L16" t="b">
         <v>0</v>
       </c>
       <c r="M16" t="s">
-        <v>900</v>
+        <v>921</v>
       </c>
       <c r="N16" t="s">
-        <v>914</v>
+        <v>935</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -4216,28 +4303,28 @@
         <v>407</v>
       </c>
       <c r="G17" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="H17" t="s">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="I17" t="s">
-        <v>722</v>
+        <v>734</v>
       </c>
       <c r="J17" t="s">
-        <v>894</v>
+        <v>916</v>
       </c>
       <c r="K17" t="s">
-        <v>897</v>
+        <v>919</v>
       </c>
       <c r="L17" t="b">
         <v>0</v>
       </c>
       <c r="M17" t="s">
-        <v>900</v>
+        <v>921</v>
       </c>
       <c r="N17" t="s">
-        <v>913</v>
+        <v>934</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -4260,28 +4347,28 @@
         <v>413</v>
       </c>
       <c r="G18" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="H18" t="s">
-        <v>575</v>
+        <v>579</v>
       </c>
       <c r="I18" t="s">
-        <v>723</v>
+        <v>735</v>
       </c>
       <c r="J18" t="s">
-        <v>895</v>
+        <v>917</v>
       </c>
       <c r="K18" t="s">
-        <v>897</v>
+        <v>919</v>
       </c>
       <c r="L18" t="b">
         <v>1</v>
       </c>
       <c r="M18" t="s">
-        <v>901</v>
+        <v>922</v>
       </c>
       <c r="N18" t="s">
-        <v>915</v>
+        <v>936</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -4304,28 +4391,28 @@
         <v>410</v>
       </c>
       <c r="G19" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="H19" t="s">
-        <v>568</v>
+        <v>572</v>
       </c>
       <c r="I19" t="s">
-        <v>724</v>
+        <v>736</v>
       </c>
       <c r="J19" t="s">
-        <v>895</v>
+        <v>917</v>
       </c>
       <c r="K19" t="s">
-        <v>898</v>
+        <v>920</v>
       </c>
       <c r="L19" t="b">
         <v>1</v>
       </c>
       <c r="M19" t="s">
-        <v>901</v>
+        <v>922</v>
       </c>
       <c r="N19" t="s">
-        <v>908</v>
+        <v>929</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -4348,28 +4435,28 @@
         <v>410</v>
       </c>
       <c r="G20" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="H20" t="s">
-        <v>568</v>
+        <v>572</v>
       </c>
       <c r="I20" t="s">
-        <v>725</v>
+        <v>737</v>
       </c>
       <c r="J20" t="s">
-        <v>894</v>
+        <v>916</v>
       </c>
       <c r="K20" t="s">
-        <v>897</v>
+        <v>919</v>
       </c>
       <c r="L20" t="b">
         <v>0</v>
       </c>
       <c r="M20" t="s">
-        <v>900</v>
+        <v>921</v>
       </c>
       <c r="N20" t="s">
-        <v>908</v>
+        <v>929</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -4392,28 +4479,28 @@
         <v>407</v>
       </c>
       <c r="G21" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="H21" t="s">
-        <v>576</v>
+        <v>580</v>
       </c>
       <c r="I21" t="s">
-        <v>726</v>
+        <v>738</v>
       </c>
       <c r="J21" t="s">
-        <v>894</v>
+        <v>916</v>
       </c>
       <c r="K21" t="s">
-        <v>897</v>
+        <v>919</v>
       </c>
       <c r="L21" t="b">
         <v>0</v>
       </c>
       <c r="M21" t="s">
-        <v>900</v>
+        <v>921</v>
       </c>
       <c r="N21" t="s">
-        <v>916</v>
+        <v>937</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -4436,28 +4523,28 @@
         <v>410</v>
       </c>
       <c r="G22" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="H22" t="s">
-        <v>568</v>
+        <v>572</v>
       </c>
       <c r="I22" t="s">
-        <v>727</v>
+        <v>739</v>
       </c>
       <c r="J22" t="s">
-        <v>895</v>
+        <v>917</v>
       </c>
       <c r="K22" t="s">
-        <v>898</v>
+        <v>920</v>
       </c>
       <c r="L22" t="b">
         <v>1</v>
       </c>
       <c r="M22" t="s">
-        <v>901</v>
+        <v>922</v>
       </c>
       <c r="N22" t="s">
-        <v>908</v>
+        <v>929</v>
       </c>
     </row>
     <row r="23" spans="1:14">
@@ -4480,28 +4567,28 @@
         <v>410</v>
       </c>
       <c r="G23" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="H23" t="s">
-        <v>568</v>
+        <v>572</v>
       </c>
       <c r="I23" t="s">
-        <v>728</v>
+        <v>740</v>
       </c>
       <c r="J23" t="s">
-        <v>894</v>
+        <v>916</v>
       </c>
       <c r="K23" t="s">
-        <v>897</v>
+        <v>919</v>
       </c>
       <c r="L23" t="b">
         <v>0</v>
       </c>
       <c r="M23" t="s">
-        <v>900</v>
+        <v>921</v>
       </c>
       <c r="N23" t="s">
-        <v>908</v>
+        <v>929</v>
       </c>
     </row>
     <row r="24" spans="1:14">
@@ -4524,28 +4611,28 @@
         <v>410</v>
       </c>
       <c r="G24" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="H24" t="s">
-        <v>568</v>
+        <v>572</v>
       </c>
       <c r="I24" t="s">
-        <v>729</v>
+        <v>741</v>
       </c>
       <c r="J24" t="s">
-        <v>895</v>
+        <v>917</v>
       </c>
       <c r="K24" t="s">
-        <v>898</v>
+        <v>920</v>
       </c>
       <c r="L24" t="b">
         <v>1</v>
       </c>
       <c r="M24" t="s">
-        <v>901</v>
+        <v>922</v>
       </c>
       <c r="N24" t="s">
-        <v>908</v>
+        <v>929</v>
       </c>
     </row>
     <row r="25" spans="1:14">
@@ -4568,28 +4655,28 @@
         <v>407</v>
       </c>
       <c r="G25" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="H25" t="s">
-        <v>577</v>
+        <v>581</v>
       </c>
       <c r="I25" t="s">
-        <v>730</v>
+        <v>742</v>
       </c>
       <c r="J25" t="s">
-        <v>896</v>
+        <v>918</v>
       </c>
       <c r="K25" t="s">
-        <v>898</v>
+        <v>920</v>
       </c>
       <c r="L25" t="b">
         <v>1</v>
       </c>
       <c r="M25" t="s">
-        <v>901</v>
+        <v>922</v>
       </c>
       <c r="N25" t="s">
-        <v>917</v>
+        <v>938</v>
       </c>
     </row>
     <row r="26" spans="1:14">
@@ -4612,28 +4699,28 @@
         <v>409</v>
       </c>
       <c r="G26" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="H26" t="s">
-        <v>578</v>
+        <v>582</v>
       </c>
       <c r="I26" t="s">
-        <v>731</v>
+        <v>743</v>
       </c>
       <c r="J26" t="s">
-        <v>894</v>
+        <v>916</v>
       </c>
       <c r="K26" t="s">
-        <v>897</v>
+        <v>919</v>
       </c>
       <c r="L26" t="b">
         <v>0</v>
       </c>
       <c r="M26" t="s">
-        <v>900</v>
+        <v>921</v>
       </c>
       <c r="N26" t="s">
-        <v>918</v>
+        <v>939</v>
       </c>
     </row>
     <row r="27" spans="1:14">
@@ -4656,28 +4743,28 @@
         <v>414</v>
       </c>
       <c r="G27" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H27" t="s">
-        <v>579</v>
+        <v>583</v>
       </c>
       <c r="I27" t="s">
-        <v>732</v>
+        <v>744</v>
       </c>
       <c r="J27" t="s">
-        <v>894</v>
+        <v>916</v>
       </c>
       <c r="K27" t="s">
-        <v>897</v>
+        <v>919</v>
       </c>
       <c r="L27" t="b">
         <v>0</v>
       </c>
       <c r="M27" t="s">
-        <v>900</v>
+        <v>921</v>
       </c>
       <c r="N27" t="s">
-        <v>919</v>
+        <v>940</v>
       </c>
     </row>
     <row r="28" spans="1:14">
@@ -4700,28 +4787,28 @@
         <v>413</v>
       </c>
       <c r="G28" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H28" t="s">
-        <v>580</v>
+        <v>584</v>
       </c>
       <c r="I28" t="s">
-        <v>733</v>
+        <v>745</v>
       </c>
       <c r="J28" t="s">
-        <v>894</v>
+        <v>916</v>
       </c>
       <c r="K28" t="s">
-        <v>897</v>
+        <v>919</v>
       </c>
       <c r="L28" t="b">
         <v>0</v>
       </c>
       <c r="M28" t="s">
-        <v>900</v>
+        <v>921</v>
       </c>
       <c r="N28" t="s">
-        <v>920</v>
+        <v>941</v>
       </c>
     </row>
     <row r="29" spans="1:14">
@@ -4744,28 +4831,28 @@
         <v>415</v>
       </c>
       <c r="G29" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H29" t="s">
-        <v>581</v>
+        <v>585</v>
       </c>
       <c r="I29" t="s">
-        <v>734</v>
+        <v>746</v>
       </c>
       <c r="J29" t="s">
-        <v>894</v>
+        <v>916</v>
       </c>
       <c r="K29" t="s">
-        <v>897</v>
+        <v>919</v>
       </c>
       <c r="L29" t="b">
         <v>0</v>
       </c>
       <c r="M29" t="s">
-        <v>900</v>
+        <v>921</v>
       </c>
       <c r="N29" t="s">
-        <v>921</v>
+        <v>942</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -4788,28 +4875,28 @@
         <v>414</v>
       </c>
       <c r="G30" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H30" t="s">
-        <v>582</v>
+        <v>586</v>
       </c>
       <c r="I30" t="s">
-        <v>735</v>
+        <v>747</v>
       </c>
       <c r="J30" t="s">
-        <v>894</v>
+        <v>916</v>
       </c>
       <c r="K30" t="s">
-        <v>897</v>
+        <v>919</v>
       </c>
       <c r="L30" t="b">
         <v>0</v>
       </c>
       <c r="M30" t="s">
-        <v>900</v>
+        <v>921</v>
       </c>
       <c r="N30" t="s">
-        <v>922</v>
+        <v>943</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -4832,28 +4919,28 @@
         <v>414</v>
       </c>
       <c r="G31" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H31" t="s">
-        <v>583</v>
+        <v>587</v>
       </c>
       <c r="I31" t="s">
-        <v>736</v>
+        <v>748</v>
       </c>
       <c r="J31" t="s">
-        <v>894</v>
+        <v>916</v>
       </c>
       <c r="K31" t="s">
-        <v>897</v>
+        <v>919</v>
       </c>
       <c r="L31" t="b">
         <v>0</v>
       </c>
       <c r="M31" t="s">
-        <v>900</v>
+        <v>921</v>
       </c>
       <c r="N31" t="s">
-        <v>923</v>
+        <v>944</v>
       </c>
     </row>
     <row r="32" spans="1:14">
@@ -4876,28 +4963,28 @@
         <v>416</v>
       </c>
       <c r="G32" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H32" t="s">
-        <v>584</v>
+        <v>588</v>
       </c>
       <c r="I32" t="s">
-        <v>737</v>
+        <v>749</v>
       </c>
       <c r="J32" t="s">
-        <v>894</v>
+        <v>916</v>
       </c>
       <c r="K32" t="s">
-        <v>897</v>
+        <v>919</v>
       </c>
       <c r="L32" t="b">
         <v>0</v>
       </c>
       <c r="M32" t="s">
-        <v>900</v>
+        <v>921</v>
       </c>
       <c r="N32" t="s">
-        <v>924</v>
+        <v>945</v>
       </c>
     </row>
     <row r="33" spans="1:14">
@@ -4920,28 +5007,28 @@
         <v>414</v>
       </c>
       <c r="G33" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="H33" t="s">
-        <v>585</v>
+        <v>589</v>
       </c>
       <c r="I33" t="s">
-        <v>738</v>
+        <v>750</v>
       </c>
       <c r="J33" t="s">
-        <v>894</v>
+        <v>916</v>
       </c>
       <c r="K33" t="s">
-        <v>897</v>
+        <v>919</v>
       </c>
       <c r="L33" t="b">
         <v>0</v>
       </c>
       <c r="M33" t="s">
-        <v>900</v>
+        <v>921</v>
       </c>
       <c r="N33" t="s">
-        <v>925</v>
+        <v>946</v>
       </c>
     </row>
     <row r="34" spans="1:14">
@@ -4964,28 +5051,28 @@
         <v>414</v>
       </c>
       <c r="G34" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H34" t="s">
-        <v>586</v>
+        <v>590</v>
       </c>
       <c r="I34" t="s">
-        <v>739</v>
+        <v>751</v>
       </c>
       <c r="J34" t="s">
-        <v>894</v>
+        <v>916</v>
       </c>
       <c r="K34" t="s">
-        <v>897</v>
+        <v>919</v>
       </c>
       <c r="L34" t="b">
         <v>0</v>
       </c>
       <c r="M34" t="s">
-        <v>900</v>
+        <v>921</v>
       </c>
       <c r="N34" t="s">
-        <v>926</v>
+        <v>947</v>
       </c>
     </row>
     <row r="35" spans="1:14">
@@ -5008,28 +5095,28 @@
         <v>414</v>
       </c>
       <c r="G35" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H35" t="s">
-        <v>587</v>
+        <v>591</v>
       </c>
       <c r="I35" t="s">
-        <v>740</v>
+        <v>752</v>
       </c>
       <c r="J35" t="s">
-        <v>894</v>
+        <v>916</v>
       </c>
       <c r="K35" t="s">
-        <v>897</v>
+        <v>919</v>
       </c>
       <c r="L35" t="b">
         <v>0</v>
       </c>
       <c r="M35" t="s">
-        <v>900</v>
+        <v>921</v>
       </c>
       <c r="N35" t="s">
-        <v>927</v>
+        <v>948</v>
       </c>
     </row>
     <row r="36" spans="1:14">
@@ -5052,28 +5139,28 @@
         <v>415</v>
       </c>
       <c r="G36" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H36" t="s">
-        <v>581</v>
+        <v>585</v>
       </c>
       <c r="I36" t="s">
-        <v>741</v>
+        <v>753</v>
       </c>
       <c r="J36" t="s">
-        <v>895</v>
+        <v>917</v>
       </c>
       <c r="K36" t="s">
-        <v>898</v>
+        <v>920</v>
       </c>
       <c r="L36" t="b">
         <v>1</v>
       </c>
       <c r="M36" t="s">
-        <v>901</v>
+        <v>922</v>
       </c>
       <c r="N36" t="s">
-        <v>921</v>
+        <v>942</v>
       </c>
     </row>
     <row r="37" spans="1:14">
@@ -5096,28 +5183,28 @@
         <v>415</v>
       </c>
       <c r="G37" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H37" t="s">
-        <v>588</v>
+        <v>592</v>
       </c>
       <c r="I37" t="s">
-        <v>742</v>
+        <v>754</v>
       </c>
       <c r="J37" t="s">
-        <v>894</v>
+        <v>916</v>
       </c>
       <c r="K37" t="s">
-        <v>897</v>
+        <v>919</v>
       </c>
       <c r="L37" t="b">
         <v>0</v>
       </c>
       <c r="M37" t="s">
-        <v>900</v>
+        <v>921</v>
       </c>
       <c r="N37" t="s">
-        <v>928</v>
+        <v>949</v>
       </c>
     </row>
     <row r="38" spans="1:14">
@@ -5140,28 +5227,28 @@
         <v>417</v>
       </c>
       <c r="G38" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H38" t="s">
-        <v>589</v>
+        <v>593</v>
       </c>
       <c r="I38" t="s">
-        <v>743</v>
+        <v>755</v>
       </c>
       <c r="J38" t="s">
-        <v>894</v>
+        <v>916</v>
       </c>
       <c r="K38" t="s">
-        <v>897</v>
+        <v>919</v>
       </c>
       <c r="L38" t="b">
         <v>0</v>
       </c>
       <c r="M38" t="s">
-        <v>900</v>
+        <v>921</v>
       </c>
       <c r="N38" t="s">
-        <v>929</v>
+        <v>950</v>
       </c>
     </row>
     <row r="39" spans="1:14">
@@ -5184,28 +5271,28 @@
         <v>418</v>
       </c>
       <c r="G39" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="H39" t="s">
-        <v>590</v>
+        <v>594</v>
       </c>
       <c r="I39" t="s">
-        <v>744</v>
+        <v>756</v>
       </c>
       <c r="J39" t="s">
-        <v>894</v>
+        <v>916</v>
       </c>
       <c r="K39" t="s">
-        <v>897</v>
+        <v>919</v>
       </c>
       <c r="L39" t="b">
         <v>0</v>
       </c>
       <c r="M39" t="s">
-        <v>900</v>
+        <v>921</v>
       </c>
       <c r="N39" t="s">
-        <v>930</v>
+        <v>951</v>
       </c>
     </row>
     <row r="40" spans="1:14">
@@ -5228,28 +5315,28 @@
         <v>417</v>
       </c>
       <c r="G40" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H40" t="s">
-        <v>591</v>
+        <v>595</v>
       </c>
       <c r="I40" t="s">
-        <v>745</v>
+        <v>757</v>
       </c>
       <c r="J40" t="s">
-        <v>894</v>
+        <v>916</v>
       </c>
       <c r="K40" t="s">
-        <v>897</v>
+        <v>919</v>
       </c>
       <c r="L40" t="b">
         <v>0</v>
       </c>
       <c r="M40" t="s">
-        <v>900</v>
+        <v>921</v>
       </c>
       <c r="N40" t="s">
-        <v>931</v>
+        <v>952</v>
       </c>
     </row>
     <row r="41" spans="1:14">
@@ -5272,28 +5359,28 @@
         <v>419</v>
       </c>
       <c r="G41" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H41" t="s">
-        <v>592</v>
+        <v>596</v>
       </c>
       <c r="I41" t="s">
-        <v>746</v>
+        <v>758</v>
       </c>
       <c r="J41" t="s">
-        <v>894</v>
+        <v>916</v>
       </c>
       <c r="K41" t="s">
-        <v>897</v>
+        <v>919</v>
       </c>
       <c r="L41" t="b">
         <v>0</v>
       </c>
       <c r="M41" t="s">
-        <v>900</v>
+        <v>921</v>
       </c>
       <c r="N41" t="s">
-        <v>932</v>
+        <v>953</v>
       </c>
     </row>
     <row r="42" spans="1:14">
@@ -5316,28 +5403,28 @@
         <v>418</v>
       </c>
       <c r="G42" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="H42" t="s">
-        <v>593</v>
+        <v>597</v>
       </c>
       <c r="I42" t="s">
-        <v>747</v>
+        <v>759</v>
       </c>
       <c r="J42" t="s">
-        <v>894</v>
+        <v>916</v>
       </c>
       <c r="K42" t="s">
-        <v>897</v>
+        <v>919</v>
       </c>
       <c r="L42" t="b">
         <v>0</v>
       </c>
       <c r="M42" t="s">
-        <v>900</v>
+        <v>921</v>
       </c>
       <c r="N42" t="s">
-        <v>933</v>
+        <v>954</v>
       </c>
     </row>
     <row r="43" spans="1:14">
@@ -5360,28 +5447,28 @@
         <v>417</v>
       </c>
       <c r="G43" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H43" t="s">
-        <v>594</v>
+        <v>598</v>
       </c>
       <c r="I43" t="s">
-        <v>748</v>
+        <v>760</v>
       </c>
       <c r="J43" t="s">
-        <v>894</v>
+        <v>916</v>
       </c>
       <c r="K43" t="s">
-        <v>897</v>
+        <v>919</v>
       </c>
       <c r="L43" t="b">
         <v>0</v>
       </c>
       <c r="M43" t="s">
-        <v>900</v>
+        <v>921</v>
       </c>
       <c r="N43" t="s">
-        <v>934</v>
+        <v>955</v>
       </c>
     </row>
     <row r="44" spans="1:14">
@@ -5404,28 +5491,28 @@
         <v>416</v>
       </c>
       <c r="G44" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="H44" t="s">
-        <v>595</v>
+        <v>599</v>
       </c>
       <c r="I44" t="s">
-        <v>749</v>
+        <v>761</v>
       </c>
       <c r="J44" t="s">
-        <v>894</v>
+        <v>916</v>
       </c>
       <c r="K44" t="s">
-        <v>897</v>
+        <v>919</v>
       </c>
       <c r="L44" t="b">
         <v>0</v>
       </c>
       <c r="M44" t="s">
-        <v>900</v>
+        <v>921</v>
       </c>
       <c r="N44" t="s">
-        <v>935</v>
+        <v>956</v>
       </c>
     </row>
     <row r="45" spans="1:14">
@@ -5448,28 +5535,28 @@
         <v>414</v>
       </c>
       <c r="G45" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H45" t="s">
-        <v>596</v>
+        <v>600</v>
       </c>
       <c r="I45" t="s">
-        <v>750</v>
+        <v>762</v>
       </c>
       <c r="J45" t="s">
-        <v>894</v>
+        <v>916</v>
       </c>
       <c r="K45" t="s">
-        <v>897</v>
+        <v>919</v>
       </c>
       <c r="L45" t="b">
         <v>0</v>
       </c>
       <c r="M45" t="s">
-        <v>900</v>
+        <v>921</v>
       </c>
       <c r="N45" t="s">
-        <v>936</v>
+        <v>957</v>
       </c>
     </row>
     <row r="46" spans="1:14">
@@ -5492,28 +5579,28 @@
         <v>420</v>
       </c>
       <c r="G46" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H46" t="s">
-        <v>597</v>
+        <v>601</v>
       </c>
       <c r="I46" t="s">
-        <v>751</v>
+        <v>763</v>
       </c>
       <c r="J46" t="s">
-        <v>894</v>
+        <v>916</v>
       </c>
       <c r="K46" t="s">
-        <v>897</v>
+        <v>919</v>
       </c>
       <c r="L46" t="b">
         <v>0</v>
       </c>
       <c r="M46" t="s">
-        <v>900</v>
+        <v>921</v>
       </c>
       <c r="N46" t="s">
-        <v>937</v>
+        <v>958</v>
       </c>
     </row>
     <row r="47" spans="1:14">
@@ -5536,28 +5623,28 @@
         <v>418</v>
       </c>
       <c r="G47" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="H47" t="s">
-        <v>598</v>
+        <v>602</v>
       </c>
       <c r="I47" t="s">
-        <v>752</v>
+        <v>764</v>
       </c>
       <c r="J47" t="s">
-        <v>894</v>
+        <v>916</v>
       </c>
       <c r="K47" t="s">
-        <v>897</v>
+        <v>919</v>
       </c>
       <c r="L47" t="b">
         <v>0</v>
       </c>
       <c r="M47" t="s">
-        <v>900</v>
+        <v>921</v>
       </c>
       <c r="N47" t="s">
-        <v>938</v>
+        <v>959</v>
       </c>
     </row>
     <row r="48" spans="1:14">
@@ -5580,28 +5667,28 @@
         <v>414</v>
       </c>
       <c r="G48" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="H48" t="s">
-        <v>599</v>
+        <v>603</v>
       </c>
       <c r="I48" t="s">
-        <v>753</v>
+        <v>765</v>
       </c>
       <c r="J48" t="s">
-        <v>894</v>
+        <v>916</v>
       </c>
       <c r="K48" t="s">
-        <v>897</v>
+        <v>919</v>
       </c>
       <c r="L48" t="b">
         <v>0</v>
       </c>
       <c r="M48" t="s">
-        <v>900</v>
+        <v>921</v>
       </c>
       <c r="N48" t="s">
-        <v>939</v>
+        <v>960</v>
       </c>
     </row>
     <row r="49" spans="1:14">
@@ -5624,28 +5711,28 @@
         <v>416</v>
       </c>
       <c r="G49" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="H49" t="s">
-        <v>600</v>
+        <v>604</v>
       </c>
       <c r="I49" t="s">
-        <v>754</v>
+        <v>766</v>
       </c>
       <c r="J49" t="s">
-        <v>896</v>
+        <v>918</v>
       </c>
       <c r="K49" t="s">
-        <v>898</v>
+        <v>920</v>
       </c>
       <c r="L49" t="b">
         <v>1</v>
       </c>
       <c r="M49" t="s">
-        <v>901</v>
+        <v>922</v>
       </c>
       <c r="N49" t="s">
-        <v>940</v>
+        <v>961</v>
       </c>
     </row>
     <row r="50" spans="1:14">
@@ -5668,28 +5755,28 @@
         <v>416</v>
       </c>
       <c r="G50" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="H50" t="s">
-        <v>600</v>
+        <v>604</v>
       </c>
       <c r="I50" t="s">
-        <v>755</v>
+        <v>767</v>
       </c>
       <c r="J50" t="s">
-        <v>894</v>
+        <v>916</v>
       </c>
       <c r="K50" t="s">
-        <v>897</v>
+        <v>919</v>
       </c>
       <c r="L50" t="b">
         <v>0</v>
       </c>
       <c r="M50" t="s">
-        <v>900</v>
+        <v>921</v>
       </c>
       <c r="N50" t="s">
-        <v>940</v>
+        <v>961</v>
       </c>
     </row>
     <row r="51" spans="1:14">
@@ -5712,28 +5799,28 @@
         <v>414</v>
       </c>
       <c r="G51" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H51" t="s">
-        <v>579</v>
+        <v>583</v>
       </c>
       <c r="I51" t="s">
-        <v>756</v>
+        <v>768</v>
       </c>
       <c r="J51" t="s">
-        <v>895</v>
+        <v>917</v>
       </c>
       <c r="K51" t="s">
-        <v>898</v>
+        <v>920</v>
       </c>
       <c r="L51" t="b">
         <v>1</v>
       </c>
       <c r="M51" t="s">
-        <v>901</v>
+        <v>922</v>
       </c>
       <c r="N51" t="s">
-        <v>919</v>
+        <v>940</v>
       </c>
     </row>
     <row r="52" spans="1:14">
@@ -5756,28 +5843,28 @@
         <v>421</v>
       </c>
       <c r="G52" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="H52" t="s">
-        <v>601</v>
+        <v>605</v>
       </c>
       <c r="I52" t="s">
-        <v>757</v>
+        <v>769</v>
       </c>
       <c r="J52" t="s">
-        <v>894</v>
+        <v>916</v>
       </c>
       <c r="K52" t="s">
-        <v>897</v>
+        <v>919</v>
       </c>
       <c r="L52" t="b">
         <v>0</v>
       </c>
       <c r="M52" t="s">
-        <v>900</v>
+        <v>921</v>
       </c>
       <c r="N52" t="s">
-        <v>941</v>
+        <v>962</v>
       </c>
     </row>
     <row r="53" spans="1:14">
@@ -5800,28 +5887,28 @@
         <v>422</v>
       </c>
       <c r="G53" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="H53" t="s">
-        <v>602</v>
+        <v>606</v>
       </c>
       <c r="I53" t="s">
-        <v>758</v>
+        <v>770</v>
       </c>
       <c r="J53" t="s">
-        <v>894</v>
+        <v>916</v>
       </c>
       <c r="K53" t="s">
-        <v>897</v>
+        <v>919</v>
       </c>
       <c r="L53" t="b">
         <v>0</v>
       </c>
       <c r="M53" t="s">
-        <v>900</v>
+        <v>921</v>
       </c>
       <c r="N53" t="s">
-        <v>942</v>
+        <v>963</v>
       </c>
     </row>
     <row r="54" spans="1:14">
@@ -5844,28 +5931,28 @@
         <v>423</v>
       </c>
       <c r="G54" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="H54" t="s">
-        <v>603</v>
+        <v>607</v>
       </c>
       <c r="I54" t="s">
-        <v>759</v>
+        <v>771</v>
       </c>
       <c r="J54" t="s">
-        <v>894</v>
+        <v>916</v>
       </c>
       <c r="K54" t="s">
-        <v>897</v>
+        <v>919</v>
       </c>
       <c r="L54" t="b">
         <v>0</v>
       </c>
       <c r="M54" t="s">
-        <v>900</v>
+        <v>921</v>
       </c>
       <c r="N54" t="s">
-        <v>943</v>
+        <v>964</v>
       </c>
     </row>
     <row r="55" spans="1:14">
@@ -5888,28 +5975,28 @@
         <v>424</v>
       </c>
       <c r="G55" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="H55" t="s">
-        <v>604</v>
+        <v>608</v>
       </c>
       <c r="I55" t="s">
-        <v>760</v>
+        <v>772</v>
       </c>
       <c r="J55" t="s">
-        <v>894</v>
+        <v>916</v>
       </c>
       <c r="K55" t="s">
-        <v>897</v>
+        <v>919</v>
       </c>
       <c r="L55" t="b">
         <v>0</v>
       </c>
       <c r="M55" t="s">
-        <v>900</v>
+        <v>921</v>
       </c>
       <c r="N55" t="s">
-        <v>944</v>
+        <v>965</v>
       </c>
     </row>
     <row r="56" spans="1:14">
@@ -5932,28 +6019,28 @@
         <v>424</v>
       </c>
       <c r="G56" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="H56" t="s">
-        <v>605</v>
+        <v>609</v>
       </c>
       <c r="I56" t="s">
-        <v>761</v>
+        <v>773</v>
       </c>
       <c r="J56" t="s">
-        <v>894</v>
+        <v>916</v>
       </c>
       <c r="K56" t="s">
-        <v>897</v>
+        <v>919</v>
       </c>
       <c r="L56" t="b">
         <v>0</v>
       </c>
       <c r="M56" t="s">
-        <v>900</v>
+        <v>921</v>
       </c>
       <c r="N56" t="s">
-        <v>945</v>
+        <v>966</v>
       </c>
     </row>
     <row r="57" spans="1:14">
@@ -5976,28 +6063,28 @@
         <v>423</v>
       </c>
       <c r="G57" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="H57" t="s">
-        <v>606</v>
+        <v>610</v>
       </c>
       <c r="I57" t="s">
-        <v>762</v>
+        <v>774</v>
       </c>
       <c r="J57" t="s">
-        <v>894</v>
+        <v>916</v>
       </c>
       <c r="K57" t="s">
-        <v>897</v>
+        <v>919</v>
       </c>
       <c r="L57" t="b">
         <v>0</v>
       </c>
       <c r="M57" t="s">
-        <v>900</v>
+        <v>921</v>
       </c>
       <c r="N57" t="s">
-        <v>946</v>
+        <v>967</v>
       </c>
     </row>
     <row r="58" spans="1:14">
@@ -6020,28 +6107,28 @@
         <v>421</v>
       </c>
       <c r="G58" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="H58" t="s">
-        <v>607</v>
+        <v>611</v>
       </c>
       <c r="I58" t="s">
-        <v>763</v>
+        <v>775</v>
       </c>
       <c r="J58" t="s">
-        <v>895</v>
+        <v>917</v>
       </c>
       <c r="K58" t="s">
-        <v>897</v>
+        <v>919</v>
       </c>
       <c r="L58" t="b">
         <v>1</v>
       </c>
       <c r="M58" t="s">
-        <v>901</v>
+        <v>922</v>
       </c>
       <c r="N58" t="s">
-        <v>947</v>
+        <v>968</v>
       </c>
     </row>
     <row r="59" spans="1:14">
@@ -6064,28 +6151,28 @@
         <v>410</v>
       </c>
       <c r="G59" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="H59" t="s">
-        <v>568</v>
+        <v>572</v>
       </c>
       <c r="I59" t="s">
-        <v>764</v>
+        <v>776</v>
       </c>
       <c r="J59" t="s">
-        <v>894</v>
+        <v>916</v>
       </c>
       <c r="K59" t="s">
-        <v>897</v>
+        <v>919</v>
       </c>
       <c r="L59" t="b">
         <v>0</v>
       </c>
       <c r="M59" t="s">
-        <v>900</v>
+        <v>921</v>
       </c>
       <c r="N59" t="s">
-        <v>908</v>
+        <v>929</v>
       </c>
     </row>
     <row r="60" spans="1:14">
@@ -6108,28 +6195,28 @@
         <v>424</v>
       </c>
       <c r="G60" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="H60" t="s">
-        <v>608</v>
+        <v>612</v>
       </c>
       <c r="I60" t="s">
-        <v>765</v>
+        <v>777</v>
       </c>
       <c r="J60" t="s">
-        <v>894</v>
+        <v>916</v>
       </c>
       <c r="K60" t="s">
-        <v>897</v>
+        <v>919</v>
       </c>
       <c r="L60" t="b">
         <v>0</v>
       </c>
       <c r="M60" t="s">
-        <v>900</v>
+        <v>921</v>
       </c>
       <c r="N60" t="s">
-        <v>948</v>
+        <v>969</v>
       </c>
     </row>
     <row r="61" spans="1:14">
@@ -6152,28 +6239,28 @@
         <v>425</v>
       </c>
       <c r="G61" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="H61" t="s">
-        <v>609</v>
+        <v>613</v>
       </c>
       <c r="I61" t="s">
-        <v>766</v>
+        <v>778</v>
       </c>
       <c r="J61" t="s">
-        <v>894</v>
+        <v>916</v>
       </c>
       <c r="K61" t="s">
-        <v>897</v>
+        <v>919</v>
       </c>
       <c r="L61" t="b">
         <v>0</v>
       </c>
       <c r="M61" t="s">
-        <v>900</v>
+        <v>921</v>
       </c>
       <c r="N61" t="s">
-        <v>949</v>
+        <v>970</v>
       </c>
     </row>
     <row r="62" spans="1:14">
@@ -6196,28 +6283,28 @@
         <v>423</v>
       </c>
       <c r="G62" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="H62" t="s">
-        <v>610</v>
+        <v>614</v>
       </c>
       <c r="I62" t="s">
-        <v>767</v>
+        <v>779</v>
       </c>
       <c r="J62" t="s">
-        <v>894</v>
+        <v>916</v>
       </c>
       <c r="K62" t="s">
-        <v>897</v>
+        <v>919</v>
       </c>
       <c r="L62" t="b">
         <v>0</v>
       </c>
       <c r="M62" t="s">
-        <v>900</v>
+        <v>921</v>
       </c>
       <c r="N62" t="s">
-        <v>950</v>
+        <v>971</v>
       </c>
     </row>
     <row r="63" spans="1:14">
@@ -6240,28 +6327,28 @@
         <v>422</v>
       </c>
       <c r="G63" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="H63" t="s">
-        <v>602</v>
+        <v>606</v>
       </c>
       <c r="I63" t="s">
-        <v>768</v>
+        <v>780</v>
       </c>
       <c r="J63" t="s">
-        <v>896</v>
+        <v>918</v>
       </c>
       <c r="K63" t="s">
-        <v>898</v>
+        <v>920</v>
       </c>
       <c r="L63" t="b">
         <v>1</v>
       </c>
       <c r="M63" t="s">
-        <v>901</v>
+        <v>922</v>
       </c>
       <c r="N63" t="s">
-        <v>942</v>
+        <v>963</v>
       </c>
     </row>
     <row r="64" spans="1:14">
@@ -6284,28 +6371,28 @@
         <v>422</v>
       </c>
       <c r="G64" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="H64" t="s">
-        <v>611</v>
+        <v>615</v>
       </c>
       <c r="I64" t="s">
-        <v>769</v>
+        <v>781</v>
       </c>
       <c r="J64" t="s">
-        <v>894</v>
+        <v>916</v>
       </c>
       <c r="K64" t="s">
-        <v>897</v>
+        <v>919</v>
       </c>
       <c r="L64" t="b">
         <v>0</v>
       </c>
       <c r="M64" t="s">
-        <v>900</v>
+        <v>921</v>
       </c>
       <c r="N64" t="s">
-        <v>951</v>
+        <v>972</v>
       </c>
     </row>
     <row r="65" spans="1:14">
@@ -6328,28 +6415,28 @@
         <v>426</v>
       </c>
       <c r="G65" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="H65" t="s">
-        <v>612</v>
+        <v>616</v>
       </c>
       <c r="I65" t="s">
-        <v>770</v>
+        <v>782</v>
       </c>
       <c r="J65" t="s">
-        <v>894</v>
+        <v>916</v>
       </c>
       <c r="K65" t="s">
-        <v>897</v>
+        <v>919</v>
       </c>
       <c r="L65" t="b">
         <v>0</v>
       </c>
       <c r="M65" t="s">
-        <v>900</v>
+        <v>921</v>
       </c>
       <c r="N65" t="s">
-        <v>952</v>
+        <v>973</v>
       </c>
     </row>
     <row r="66" spans="1:14">
@@ -6372,28 +6459,28 @@
         <v>422</v>
       </c>
       <c r="G66" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H66" t="s">
-        <v>613</v>
+        <v>617</v>
       </c>
       <c r="I66" t="s">
-        <v>771</v>
+        <v>783</v>
       </c>
       <c r="J66" t="s">
-        <v>894</v>
+        <v>916</v>
       </c>
       <c r="K66" t="s">
-        <v>897</v>
+        <v>919</v>
       </c>
       <c r="L66" t="b">
         <v>0</v>
       </c>
       <c r="M66" t="s">
-        <v>900</v>
+        <v>921</v>
       </c>
       <c r="N66" t="s">
-        <v>953</v>
+        <v>974</v>
       </c>
     </row>
     <row r="67" spans="1:14">
@@ -6416,28 +6503,28 @@
         <v>427</v>
       </c>
       <c r="G67" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="H67" t="s">
-        <v>614</v>
+        <v>618</v>
       </c>
       <c r="I67" t="s">
-        <v>772</v>
+        <v>784</v>
       </c>
       <c r="J67" t="s">
-        <v>894</v>
+        <v>916</v>
       </c>
       <c r="K67" t="s">
-        <v>897</v>
+        <v>919</v>
       </c>
       <c r="L67" t="b">
         <v>0</v>
       </c>
       <c r="M67" t="s">
-        <v>900</v>
+        <v>921</v>
       </c>
       <c r="N67" t="s">
-        <v>954</v>
+        <v>975</v>
       </c>
     </row>
     <row r="68" spans="1:14">
@@ -6460,28 +6547,28 @@
         <v>424</v>
       </c>
       <c r="G68" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="H68" t="s">
-        <v>604</v>
+        <v>608</v>
       </c>
       <c r="I68" t="s">
-        <v>773</v>
+        <v>785</v>
       </c>
       <c r="J68" t="s">
-        <v>894</v>
+        <v>916</v>
       </c>
       <c r="K68" t="s">
-        <v>897</v>
+        <v>919</v>
       </c>
       <c r="L68" t="b">
         <v>0</v>
       </c>
       <c r="M68" t="s">
-        <v>900</v>
+        <v>921</v>
       </c>
       <c r="N68" t="s">
-        <v>944</v>
+        <v>965</v>
       </c>
     </row>
     <row r="69" spans="1:14">
@@ -6504,28 +6591,28 @@
         <v>410</v>
       </c>
       <c r="G69" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="H69" t="s">
-        <v>568</v>
+        <v>572</v>
       </c>
       <c r="I69" t="s">
-        <v>774</v>
+        <v>786</v>
       </c>
       <c r="J69" t="s">
-        <v>894</v>
+        <v>916</v>
       </c>
       <c r="K69" t="s">
-        <v>897</v>
+        <v>919</v>
       </c>
       <c r="L69" t="b">
         <v>0</v>
       </c>
       <c r="M69" t="s">
-        <v>900</v>
+        <v>921</v>
       </c>
       <c r="N69" t="s">
-        <v>908</v>
+        <v>929</v>
       </c>
     </row>
     <row r="70" spans="1:14">
@@ -6548,28 +6635,28 @@
         <v>424</v>
       </c>
       <c r="G70" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="H70" t="s">
-        <v>615</v>
+        <v>619</v>
       </c>
       <c r="I70" t="s">
-        <v>775</v>
+        <v>787</v>
       </c>
       <c r="J70" t="s">
-        <v>894</v>
+        <v>916</v>
       </c>
       <c r="K70" t="s">
-        <v>897</v>
+        <v>919</v>
       </c>
       <c r="L70" t="b">
         <v>0</v>
       </c>
       <c r="M70" t="s">
-        <v>900</v>
+        <v>921</v>
       </c>
       <c r="N70" t="s">
-        <v>955</v>
+        <v>976</v>
       </c>
     </row>
     <row r="71" spans="1:14">
@@ -6592,28 +6679,28 @@
         <v>421</v>
       </c>
       <c r="G71" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="H71" t="s">
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="I71" t="s">
-        <v>776</v>
+        <v>788</v>
       </c>
       <c r="J71" t="s">
-        <v>894</v>
+        <v>916</v>
       </c>
       <c r="K71" t="s">
-        <v>897</v>
+        <v>919</v>
       </c>
       <c r="L71" t="b">
         <v>0</v>
       </c>
       <c r="M71" t="s">
-        <v>900</v>
+        <v>921</v>
       </c>
       <c r="N71" t="s">
-        <v>956</v>
+        <v>977</v>
       </c>
     </row>
     <row r="72" spans="1:14">
@@ -6636,28 +6723,28 @@
         <v>421</v>
       </c>
       <c r="G72" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="H72" t="s">
-        <v>617</v>
+        <v>621</v>
       </c>
       <c r="I72" t="s">
-        <v>777</v>
+        <v>789</v>
       </c>
       <c r="J72" t="s">
-        <v>894</v>
+        <v>916</v>
       </c>
       <c r="K72" t="s">
-        <v>897</v>
+        <v>919</v>
       </c>
       <c r="L72" t="b">
         <v>0</v>
       </c>
       <c r="M72" t="s">
-        <v>900</v>
+        <v>921</v>
       </c>
       <c r="N72" t="s">
-        <v>957</v>
+        <v>978</v>
       </c>
     </row>
     <row r="73" spans="1:14">
@@ -6680,28 +6767,28 @@
         <v>424</v>
       </c>
       <c r="G73" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="H73" t="s">
-        <v>608</v>
+        <v>612</v>
       </c>
       <c r="I73" t="s">
-        <v>778</v>
+        <v>790</v>
       </c>
       <c r="J73" t="s">
-        <v>894</v>
+        <v>916</v>
       </c>
       <c r="K73" t="s">
-        <v>897</v>
+        <v>919</v>
       </c>
       <c r="L73" t="b">
         <v>0</v>
       </c>
       <c r="M73" t="s">
-        <v>900</v>
+        <v>921</v>
       </c>
       <c r="N73" t="s">
-        <v>948</v>
+        <v>969</v>
       </c>
     </row>
     <row r="74" spans="1:14">
@@ -6724,28 +6811,28 @@
         <v>428</v>
       </c>
       <c r="G74" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="H74" t="s">
-        <v>618</v>
+        <v>622</v>
       </c>
       <c r="I74" t="s">
-        <v>779</v>
+        <v>791</v>
       </c>
       <c r="J74" t="s">
-        <v>894</v>
+        <v>916</v>
       </c>
       <c r="K74" t="s">
-        <v>897</v>
+        <v>919</v>
       </c>
       <c r="L74" t="b">
         <v>0</v>
       </c>
       <c r="M74" t="s">
-        <v>900</v>
+        <v>921</v>
       </c>
       <c r="N74" t="s">
-        <v>958</v>
+        <v>979</v>
       </c>
     </row>
     <row r="75" spans="1:14">
@@ -6768,28 +6855,28 @@
         <v>429</v>
       </c>
       <c r="G75" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H75" t="s">
-        <v>619</v>
+        <v>623</v>
       </c>
       <c r="I75" t="s">
-        <v>780</v>
+        <v>792</v>
       </c>
       <c r="J75" t="s">
-        <v>894</v>
+        <v>916</v>
       </c>
       <c r="K75" t="s">
-        <v>897</v>
+        <v>919</v>
       </c>
       <c r="L75" t="b">
         <v>0</v>
       </c>
       <c r="M75" t="s">
-        <v>900</v>
+        <v>921</v>
       </c>
       <c r="N75" t="s">
-        <v>959</v>
+        <v>980</v>
       </c>
     </row>
     <row r="76" spans="1:14">
@@ -6812,28 +6899,28 @@
         <v>430</v>
       </c>
       <c r="G76" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H76" t="s">
-        <v>620</v>
+        <v>624</v>
       </c>
       <c r="I76" t="s">
-        <v>781</v>
+        <v>793</v>
       </c>
       <c r="J76" t="s">
-        <v>895</v>
+        <v>917</v>
       </c>
       <c r="K76" t="s">
-        <v>897</v>
+        <v>919</v>
       </c>
       <c r="L76" t="b">
         <v>1</v>
       </c>
       <c r="M76" t="s">
-        <v>901</v>
+        <v>922</v>
       </c>
       <c r="N76" t="s">
-        <v>960</v>
+        <v>981</v>
       </c>
     </row>
     <row r="77" spans="1:14">
@@ -6856,28 +6943,28 @@
         <v>430</v>
       </c>
       <c r="G77" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="H77" t="s">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="I77" t="s">
-        <v>782</v>
+        <v>794</v>
       </c>
       <c r="J77" t="s">
-        <v>894</v>
+        <v>916</v>
       </c>
       <c r="K77" t="s">
-        <v>897</v>
+        <v>919</v>
       </c>
       <c r="L77" t="b">
         <v>0</v>
       </c>
       <c r="M77" t="s">
-        <v>900</v>
+        <v>921</v>
       </c>
       <c r="N77" t="s">
-        <v>961</v>
+        <v>982</v>
       </c>
     </row>
     <row r="78" spans="1:14">
@@ -6900,28 +6987,28 @@
         <v>430</v>
       </c>
       <c r="G78" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="H78" t="s">
-        <v>622</v>
+        <v>626</v>
       </c>
       <c r="I78" t="s">
-        <v>783</v>
+        <v>795</v>
       </c>
       <c r="J78" t="s">
-        <v>894</v>
+        <v>916</v>
       </c>
       <c r="K78" t="s">
-        <v>897</v>
+        <v>919</v>
       </c>
       <c r="L78" t="b">
         <v>0</v>
       </c>
       <c r="M78" t="s">
-        <v>900</v>
+        <v>921</v>
       </c>
       <c r="N78" t="s">
-        <v>962</v>
+        <v>983</v>
       </c>
     </row>
     <row r="79" spans="1:14">
@@ -6944,28 +7031,28 @@
         <v>430</v>
       </c>
       <c r="G79" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="H79" t="s">
-        <v>623</v>
+        <v>627</v>
       </c>
       <c r="I79" t="s">
-        <v>784</v>
+        <v>796</v>
       </c>
       <c r="J79" t="s">
-        <v>894</v>
+        <v>916</v>
       </c>
       <c r="K79" t="s">
-        <v>897</v>
+        <v>919</v>
       </c>
       <c r="L79" t="b">
         <v>0</v>
       </c>
       <c r="M79" t="s">
-        <v>900</v>
+        <v>921</v>
       </c>
       <c r="N79" t="s">
-        <v>963</v>
+        <v>984</v>
       </c>
     </row>
     <row r="80" spans="1:14">
@@ -6988,28 +7075,28 @@
         <v>429</v>
       </c>
       <c r="G80" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="H80" t="s">
-        <v>624</v>
+        <v>628</v>
       </c>
       <c r="I80" t="s">
-        <v>785</v>
+        <v>797</v>
       </c>
       <c r="J80" t="s">
-        <v>895</v>
+        <v>917</v>
       </c>
       <c r="K80" t="s">
-        <v>898</v>
+        <v>920</v>
       </c>
       <c r="L80" t="b">
         <v>1</v>
       </c>
       <c r="M80" t="s">
-        <v>901</v>
+        <v>922</v>
       </c>
       <c r="N80" t="s">
-        <v>964</v>
+        <v>985</v>
       </c>
     </row>
     <row r="81" spans="1:14">
@@ -7032,28 +7119,28 @@
         <v>430</v>
       </c>
       <c r="G81" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H81" t="s">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="I81" t="s">
-        <v>786</v>
+        <v>798</v>
       </c>
       <c r="J81" t="s">
-        <v>894</v>
+        <v>916</v>
       </c>
       <c r="K81" t="s">
-        <v>897</v>
+        <v>919</v>
       </c>
       <c r="L81" t="b">
         <v>0</v>
       </c>
       <c r="M81" t="s">
-        <v>900</v>
+        <v>921</v>
       </c>
       <c r="N81" t="s">
-        <v>965</v>
+        <v>986</v>
       </c>
     </row>
     <row r="82" spans="1:14">
@@ -7076,28 +7163,28 @@
         <v>431</v>
       </c>
       <c r="G82" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="H82" t="s">
-        <v>626</v>
+        <v>630</v>
       </c>
       <c r="I82" t="s">
-        <v>787</v>
+        <v>799</v>
       </c>
       <c r="J82" t="s">
-        <v>894</v>
+        <v>916</v>
       </c>
       <c r="K82" t="s">
-        <v>897</v>
+        <v>919</v>
       </c>
       <c r="L82" t="b">
         <v>0</v>
       </c>
       <c r="M82" t="s">
-        <v>900</v>
+        <v>921</v>
       </c>
       <c r="N82" t="s">
-        <v>966</v>
+        <v>987</v>
       </c>
     </row>
     <row r="83" spans="1:14">
@@ -7120,28 +7207,28 @@
         <v>431</v>
       </c>
       <c r="G83" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="H83" t="s">
-        <v>627</v>
+        <v>631</v>
       </c>
       <c r="I83" t="s">
-        <v>788</v>
+        <v>800</v>
       </c>
       <c r="J83" t="s">
-        <v>894</v>
+        <v>916</v>
       </c>
       <c r="K83" t="s">
-        <v>897</v>
+        <v>919</v>
       </c>
       <c r="L83" t="b">
         <v>0</v>
       </c>
       <c r="M83" t="s">
-        <v>900</v>
+        <v>921</v>
       </c>
       <c r="N83" t="s">
-        <v>967</v>
+        <v>988</v>
       </c>
     </row>
     <row r="84" spans="1:14">
@@ -7164,28 +7251,28 @@
         <v>429</v>
       </c>
       <c r="G84" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="H84" t="s">
-        <v>624</v>
+        <v>628</v>
       </c>
       <c r="I84" t="s">
-        <v>789</v>
+        <v>801</v>
       </c>
       <c r="J84" t="s">
-        <v>894</v>
+        <v>916</v>
       </c>
       <c r="K84" t="s">
-        <v>897</v>
+        <v>919</v>
       </c>
       <c r="L84" t="b">
         <v>0</v>
       </c>
       <c r="M84" t="s">
-        <v>900</v>
+        <v>921</v>
       </c>
       <c r="N84" t="s">
-        <v>964</v>
+        <v>985</v>
       </c>
     </row>
     <row r="85" spans="1:14">
@@ -7208,28 +7295,28 @@
         <v>431</v>
       </c>
       <c r="G85" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="H85" t="s">
-        <v>628</v>
+        <v>632</v>
       </c>
       <c r="I85" t="s">
-        <v>790</v>
+        <v>802</v>
       </c>
       <c r="J85" t="s">
-        <v>894</v>
+        <v>916</v>
       </c>
       <c r="K85" t="s">
-        <v>897</v>
+        <v>919</v>
       </c>
       <c r="L85" t="b">
         <v>0</v>
       </c>
       <c r="M85" t="s">
-        <v>900</v>
+        <v>921</v>
       </c>
       <c r="N85" t="s">
-        <v>968</v>
+        <v>989</v>
       </c>
     </row>
     <row r="86" spans="1:14">
@@ -7252,28 +7339,28 @@
         <v>429</v>
       </c>
       <c r="G86" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H86" t="s">
-        <v>629</v>
+        <v>633</v>
       </c>
       <c r="I86" t="s">
-        <v>791</v>
+        <v>803</v>
       </c>
       <c r="J86" t="s">
-        <v>894</v>
+        <v>916</v>
       </c>
       <c r="K86" t="s">
-        <v>897</v>
+        <v>919</v>
       </c>
       <c r="L86" t="b">
         <v>0</v>
       </c>
       <c r="M86" t="s">
-        <v>900</v>
+        <v>921</v>
       </c>
       <c r="N86" t="s">
-        <v>969</v>
+        <v>990</v>
       </c>
     </row>
     <row r="87" spans="1:14">
@@ -7296,28 +7383,28 @@
         <v>418</v>
       </c>
       <c r="G87" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="H87" t="s">
-        <v>593</v>
+        <v>597</v>
       </c>
       <c r="I87" t="s">
-        <v>792</v>
+        <v>804</v>
       </c>
       <c r="J87" t="s">
-        <v>894</v>
+        <v>916</v>
       </c>
       <c r="K87" t="s">
-        <v>897</v>
+        <v>919</v>
       </c>
       <c r="L87" t="b">
         <v>0</v>
       </c>
       <c r="M87" t="s">
-        <v>900</v>
+        <v>921</v>
       </c>
       <c r="N87" t="s">
-        <v>933</v>
+        <v>954</v>
       </c>
     </row>
     <row r="88" spans="1:14">
@@ -7340,28 +7427,28 @@
         <v>432</v>
       </c>
       <c r="G88" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="H88" t="s">
-        <v>630</v>
+        <v>634</v>
       </c>
       <c r="I88" t="s">
-        <v>793</v>
+        <v>805</v>
       </c>
       <c r="J88" t="s">
-        <v>894</v>
+        <v>916</v>
       </c>
       <c r="K88" t="s">
-        <v>897</v>
+        <v>919</v>
       </c>
       <c r="L88" t="b">
         <v>0</v>
       </c>
       <c r="M88" t="s">
-        <v>900</v>
+        <v>921</v>
       </c>
       <c r="N88" t="s">
-        <v>970</v>
+        <v>991</v>
       </c>
     </row>
     <row r="89" spans="1:14">
@@ -7384,28 +7471,28 @@
         <v>429</v>
       </c>
       <c r="G89" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="H89" t="s">
-        <v>631</v>
+        <v>635</v>
       </c>
       <c r="I89" t="s">
-        <v>794</v>
+        <v>806</v>
       </c>
       <c r="J89" t="s">
-        <v>894</v>
+        <v>916</v>
       </c>
       <c r="K89" t="s">
-        <v>897</v>
+        <v>919</v>
       </c>
       <c r="L89" t="b">
         <v>0</v>
       </c>
       <c r="M89" t="s">
-        <v>900</v>
+        <v>921</v>
       </c>
       <c r="N89" t="s">
-        <v>971</v>
+        <v>992</v>
       </c>
     </row>
     <row r="90" spans="1:14">
@@ -7428,28 +7515,28 @@
         <v>430</v>
       </c>
       <c r="G90" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="H90" t="s">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="I90" t="s">
-        <v>795</v>
+        <v>807</v>
       </c>
       <c r="J90" t="s">
-        <v>895</v>
+        <v>917</v>
       </c>
       <c r="K90" t="s">
-        <v>898</v>
+        <v>920</v>
       </c>
       <c r="L90" t="b">
         <v>1</v>
       </c>
       <c r="M90" t="s">
-        <v>901</v>
+        <v>922</v>
       </c>
       <c r="N90" t="s">
-        <v>961</v>
+        <v>982</v>
       </c>
     </row>
     <row r="91" spans="1:14">
@@ -7472,28 +7559,28 @@
         <v>430</v>
       </c>
       <c r="G91" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="H91" t="s">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="I91" t="s">
-        <v>796</v>
+        <v>808</v>
       </c>
       <c r="J91" t="s">
-        <v>894</v>
+        <v>916</v>
       </c>
       <c r="K91" t="s">
-        <v>897</v>
+        <v>919</v>
       </c>
       <c r="L91" t="b">
         <v>0</v>
       </c>
       <c r="M91" t="s">
-        <v>900</v>
+        <v>921</v>
       </c>
       <c r="N91" t="s">
-        <v>961</v>
+        <v>982</v>
       </c>
     </row>
     <row r="92" spans="1:14">
@@ -7516,28 +7603,28 @@
         <v>430</v>
       </c>
       <c r="G92" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="H92" t="s">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="I92" t="s">
-        <v>797</v>
+        <v>809</v>
       </c>
       <c r="J92" t="s">
-        <v>895</v>
+        <v>917</v>
       </c>
       <c r="K92" t="s">
-        <v>897</v>
+        <v>919</v>
       </c>
       <c r="L92" t="b">
         <v>1</v>
       </c>
       <c r="M92" t="s">
-        <v>901</v>
+        <v>922</v>
       </c>
       <c r="N92" t="s">
-        <v>961</v>
+        <v>982</v>
       </c>
     </row>
     <row r="93" spans="1:14">
@@ -7560,28 +7647,28 @@
         <v>427</v>
       </c>
       <c r="G93" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="H93" t="s">
-        <v>632</v>
+        <v>636</v>
       </c>
       <c r="I93" t="s">
-        <v>798</v>
+        <v>810</v>
       </c>
       <c r="J93" t="s">
-        <v>894</v>
+        <v>916</v>
       </c>
       <c r="K93" t="s">
-        <v>897</v>
+        <v>919</v>
       </c>
       <c r="L93" t="b">
         <v>0</v>
       </c>
       <c r="M93" t="s">
-        <v>900</v>
+        <v>921</v>
       </c>
       <c r="N93" t="s">
-        <v>972</v>
+        <v>993</v>
       </c>
     </row>
     <row r="94" spans="1:14">
@@ -7604,28 +7691,28 @@
         <v>430</v>
       </c>
       <c r="G94" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="H94" t="s">
-        <v>633</v>
+        <v>637</v>
       </c>
       <c r="I94" t="s">
-        <v>799</v>
+        <v>811</v>
       </c>
       <c r="J94" t="s">
-        <v>894</v>
+        <v>916</v>
       </c>
       <c r="K94" t="s">
-        <v>897</v>
+        <v>919</v>
       </c>
       <c r="L94" t="b">
         <v>0</v>
       </c>
       <c r="M94" t="s">
-        <v>900</v>
+        <v>921</v>
       </c>
       <c r="N94" t="s">
-        <v>973</v>
+        <v>994</v>
       </c>
     </row>
     <row r="95" spans="1:14">
@@ -7648,28 +7735,28 @@
         <v>429</v>
       </c>
       <c r="G95" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="H95" t="s">
-        <v>634</v>
+        <v>638</v>
       </c>
       <c r="I95" t="s">
-        <v>800</v>
+        <v>812</v>
       </c>
       <c r="J95" t="s">
-        <v>894</v>
+        <v>916</v>
       </c>
       <c r="K95" t="s">
-        <v>897</v>
+        <v>919</v>
       </c>
       <c r="L95" t="b">
         <v>0</v>
       </c>
       <c r="M95" t="s">
-        <v>900</v>
+        <v>921</v>
       </c>
       <c r="N95" t="s">
-        <v>974</v>
+        <v>995</v>
       </c>
     </row>
     <row r="96" spans="1:14">
@@ -7692,28 +7779,28 @@
         <v>432</v>
       </c>
       <c r="G96" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="H96" t="s">
-        <v>630</v>
+        <v>634</v>
       </c>
       <c r="I96" t="s">
-        <v>801</v>
+        <v>813</v>
       </c>
       <c r="J96" t="s">
-        <v>894</v>
+        <v>916</v>
       </c>
       <c r="K96" t="s">
-        <v>897</v>
+        <v>919</v>
       </c>
       <c r="L96" t="b">
         <v>0</v>
       </c>
       <c r="M96" t="s">
-        <v>900</v>
+        <v>921</v>
       </c>
       <c r="N96" t="s">
-        <v>970</v>
+        <v>991</v>
       </c>
     </row>
     <row r="97" spans="1:14">
@@ -7736,28 +7823,28 @@
         <v>427</v>
       </c>
       <c r="G97" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="H97" t="s">
-        <v>632</v>
+        <v>636</v>
       </c>
       <c r="I97" t="s">
-        <v>802</v>
+        <v>814</v>
       </c>
       <c r="J97" t="s">
-        <v>895</v>
+        <v>917</v>
       </c>
       <c r="K97" t="s">
-        <v>898</v>
+        <v>920</v>
       </c>
       <c r="L97" t="b">
         <v>1</v>
       </c>
       <c r="M97" t="s">
-        <v>901</v>
+        <v>922</v>
       </c>
       <c r="N97" t="s">
-        <v>972</v>
+        <v>993</v>
       </c>
     </row>
     <row r="98" spans="1:14">
@@ -7780,28 +7867,28 @@
         <v>430</v>
       </c>
       <c r="G98" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H98" t="s">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="I98" t="s">
-        <v>803</v>
+        <v>815</v>
       </c>
       <c r="J98" t="s">
-        <v>894</v>
+        <v>916</v>
       </c>
       <c r="K98" t="s">
-        <v>897</v>
+        <v>919</v>
       </c>
       <c r="L98" t="b">
         <v>0</v>
       </c>
       <c r="M98" t="s">
-        <v>900</v>
+        <v>921</v>
       </c>
       <c r="N98" t="s">
-        <v>965</v>
+        <v>986</v>
       </c>
     </row>
     <row r="99" spans="1:14">
@@ -7824,28 +7911,28 @@
         <v>431</v>
       </c>
       <c r="G99" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="H99" t="s">
-        <v>635</v>
+        <v>639</v>
       </c>
       <c r="I99" t="s">
-        <v>804</v>
+        <v>816</v>
       </c>
       <c r="J99" t="s">
-        <v>894</v>
+        <v>916</v>
       </c>
       <c r="K99" t="s">
-        <v>897</v>
+        <v>919</v>
       </c>
       <c r="L99" t="b">
         <v>0</v>
       </c>
       <c r="M99" t="s">
-        <v>900</v>
+        <v>921</v>
       </c>
       <c r="N99" t="s">
-        <v>975</v>
+        <v>996</v>
       </c>
     </row>
     <row r="100" spans="1:14">
@@ -7868,28 +7955,28 @@
         <v>430</v>
       </c>
       <c r="G100" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="H100" t="s">
-        <v>636</v>
+        <v>640</v>
       </c>
       <c r="I100" t="s">
-        <v>805</v>
+        <v>817</v>
       </c>
       <c r="J100" t="s">
-        <v>894</v>
+        <v>916</v>
       </c>
       <c r="K100" t="s">
-        <v>897</v>
+        <v>919</v>
       </c>
       <c r="L100" t="b">
         <v>0</v>
       </c>
       <c r="M100" t="s">
-        <v>900</v>
+        <v>921</v>
       </c>
       <c r="N100" t="s">
-        <v>976</v>
+        <v>997</v>
       </c>
     </row>
     <row r="101" spans="1:14">
@@ -7912,28 +7999,28 @@
         <v>411</v>
       </c>
       <c r="G101" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="H101" t="s">
-        <v>637</v>
+        <v>641</v>
       </c>
       <c r="I101" t="s">
-        <v>806</v>
+        <v>818</v>
       </c>
       <c r="J101" t="s">
-        <v>895</v>
+        <v>917</v>
       </c>
       <c r="K101" t="s">
-        <v>898</v>
+        <v>920</v>
       </c>
       <c r="L101" t="b">
         <v>1</v>
       </c>
       <c r="M101" t="s">
-        <v>901</v>
+        <v>922</v>
       </c>
       <c r="N101" t="s">
-        <v>977</v>
+        <v>998</v>
       </c>
     </row>
     <row r="102" spans="1:14">
@@ -7956,28 +8043,28 @@
         <v>429</v>
       </c>
       <c r="G102" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H102" t="s">
-        <v>638</v>
+        <v>642</v>
       </c>
       <c r="I102" t="s">
-        <v>807</v>
+        <v>819</v>
       </c>
       <c r="J102" t="s">
-        <v>894</v>
+        <v>916</v>
       </c>
       <c r="K102" t="s">
-        <v>897</v>
+        <v>919</v>
       </c>
       <c r="L102" t="b">
         <v>0</v>
       </c>
       <c r="M102" t="s">
-        <v>900</v>
+        <v>921</v>
       </c>
       <c r="N102" t="s">
-        <v>978</v>
+        <v>999</v>
       </c>
     </row>
     <row r="103" spans="1:14">
@@ -8000,28 +8087,28 @@
         <v>429</v>
       </c>
       <c r="G103" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H103" t="s">
-        <v>619</v>
+        <v>623</v>
       </c>
       <c r="I103" t="s">
-        <v>808</v>
+        <v>820</v>
       </c>
       <c r="J103" t="s">
-        <v>894</v>
+        <v>916</v>
       </c>
       <c r="K103" t="s">
-        <v>897</v>
+        <v>919</v>
       </c>
       <c r="L103" t="b">
         <v>0</v>
       </c>
       <c r="M103" t="s">
-        <v>900</v>
+        <v>921</v>
       </c>
       <c r="N103" t="s">
-        <v>959</v>
+        <v>980</v>
       </c>
     </row>
     <row r="104" spans="1:14">
@@ -8044,28 +8131,28 @@
         <v>433</v>
       </c>
       <c r="G104" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="H104" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="I104" t="s">
-        <v>809</v>
+        <v>821</v>
       </c>
       <c r="J104" t="s">
-        <v>894</v>
+        <v>916</v>
       </c>
       <c r="K104" t="s">
-        <v>897</v>
+        <v>919</v>
       </c>
       <c r="L104" t="b">
         <v>0</v>
       </c>
       <c r="M104" t="s">
-        <v>900</v>
+        <v>921</v>
       </c>
       <c r="N104" t="s">
-        <v>979</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="105" spans="1:14">
@@ -8088,28 +8175,28 @@
         <v>433</v>
       </c>
       <c r="G105" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="H105" t="s">
-        <v>640</v>
+        <v>644</v>
       </c>
       <c r="I105" t="s">
-        <v>810</v>
+        <v>822</v>
       </c>
       <c r="J105" t="s">
-        <v>894</v>
+        <v>916</v>
       </c>
       <c r="K105" t="s">
-        <v>897</v>
+        <v>919</v>
       </c>
       <c r="L105" t="b">
         <v>0</v>
       </c>
       <c r="M105" t="s">
-        <v>900</v>
+        <v>921</v>
       </c>
       <c r="N105" t="s">
-        <v>980</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="106" spans="1:14">
@@ -8132,28 +8219,28 @@
         <v>434</v>
       </c>
       <c r="G106" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="H106" t="s">
-        <v>641</v>
+        <v>645</v>
       </c>
       <c r="I106" t="s">
-        <v>811</v>
+        <v>823</v>
       </c>
       <c r="J106" t="s">
-        <v>894</v>
+        <v>916</v>
       </c>
       <c r="K106" t="s">
-        <v>897</v>
+        <v>919</v>
       </c>
       <c r="L106" t="b">
         <v>0</v>
       </c>
       <c r="M106" t="s">
-        <v>900</v>
+        <v>921</v>
       </c>
       <c r="N106" t="s">
-        <v>981</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="107" spans="1:14">
@@ -8176,28 +8263,28 @@
         <v>435</v>
       </c>
       <c r="G107" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="H107" t="s">
-        <v>642</v>
+        <v>646</v>
       </c>
       <c r="I107" t="s">
-        <v>812</v>
+        <v>824</v>
       </c>
       <c r="J107" t="s">
-        <v>894</v>
+        <v>916</v>
       </c>
       <c r="K107" t="s">
-        <v>897</v>
+        <v>919</v>
       </c>
       <c r="L107" t="b">
         <v>0</v>
       </c>
       <c r="M107" t="s">
-        <v>900</v>
+        <v>921</v>
       </c>
       <c r="N107" t="s">
-        <v>982</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="108" spans="1:14">
@@ -8220,28 +8307,28 @@
         <v>435</v>
       </c>
       <c r="G108" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="H108" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="I108" t="s">
-        <v>813</v>
+        <v>825</v>
       </c>
       <c r="J108" t="s">
-        <v>894</v>
+        <v>916</v>
       </c>
       <c r="K108" t="s">
-        <v>897</v>
+        <v>919</v>
       </c>
       <c r="L108" t="b">
         <v>0</v>
       </c>
       <c r="M108" t="s">
-        <v>900</v>
+        <v>921</v>
       </c>
       <c r="N108" t="s">
-        <v>983</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="109" spans="1:14">
@@ -8264,28 +8351,28 @@
         <v>433</v>
       </c>
       <c r="G109" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="H109" t="s">
-        <v>644</v>
+        <v>648</v>
       </c>
       <c r="I109" t="s">
-        <v>814</v>
+        <v>826</v>
       </c>
       <c r="J109" t="s">
-        <v>895</v>
+        <v>917</v>
       </c>
       <c r="K109" t="s">
-        <v>898</v>
+        <v>920</v>
       </c>
       <c r="L109" t="b">
         <v>1</v>
       </c>
       <c r="M109" t="s">
-        <v>901</v>
+        <v>922</v>
       </c>
       <c r="N109" t="s">
-        <v>984</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="110" spans="1:14">
@@ -8308,28 +8395,28 @@
         <v>436</v>
       </c>
       <c r="G110" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="H110" t="s">
-        <v>645</v>
+        <v>649</v>
       </c>
       <c r="I110" t="s">
-        <v>815</v>
+        <v>827</v>
       </c>
       <c r="J110" t="s">
-        <v>894</v>
+        <v>916</v>
       </c>
       <c r="K110" t="s">
-        <v>897</v>
+        <v>919</v>
       </c>
       <c r="L110" t="b">
         <v>0</v>
       </c>
       <c r="M110" t="s">
-        <v>900</v>
+        <v>921</v>
       </c>
       <c r="N110" t="s">
-        <v>985</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="111" spans="1:14">
@@ -8352,28 +8439,28 @@
         <v>437</v>
       </c>
       <c r="G111" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="H111" t="s">
-        <v>646</v>
+        <v>650</v>
       </c>
       <c r="I111" t="s">
-        <v>816</v>
+        <v>828</v>
       </c>
       <c r="J111" t="s">
-        <v>894</v>
+        <v>916</v>
       </c>
       <c r="K111" t="s">
-        <v>897</v>
+        <v>919</v>
       </c>
       <c r="L111" t="b">
         <v>0</v>
       </c>
       <c r="M111" t="s">
-        <v>900</v>
+        <v>921</v>
       </c>
       <c r="N111" t="s">
-        <v>986</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="112" spans="1:14">
@@ -8396,28 +8483,28 @@
         <v>433</v>
       </c>
       <c r="G112" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="H112" t="s">
-        <v>647</v>
+        <v>651</v>
       </c>
       <c r="I112" t="s">
-        <v>817</v>
+        <v>829</v>
       </c>
       <c r="J112" t="s">
-        <v>894</v>
+        <v>916</v>
       </c>
       <c r="K112" t="s">
-        <v>897</v>
+        <v>919</v>
       </c>
       <c r="L112" t="b">
         <v>0</v>
       </c>
       <c r="M112" t="s">
-        <v>900</v>
+        <v>921</v>
       </c>
       <c r="N112" t="s">
-        <v>987</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="113" spans="1:14">
@@ -8433,14 +8520,35 @@
       <c r="D113" t="s">
         <v>393</v>
       </c>
+      <c r="E113" t="s">
+        <v>403</v>
+      </c>
+      <c r="F113" t="s">
+        <v>438</v>
+      </c>
+      <c r="G113" t="s">
+        <v>522</v>
+      </c>
+      <c r="H113" t="s">
+        <v>652</v>
+      </c>
+      <c r="I113" t="s">
+        <v>830</v>
+      </c>
+      <c r="J113" t="s">
+        <v>916</v>
+      </c>
       <c r="K113" t="s">
-        <v>899</v>
+        <v>919</v>
       </c>
       <c r="L113" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M113" t="s">
-        <v>899</v>
+        <v>921</v>
+      </c>
+      <c r="N113" t="s">
+        <v>1009</v>
       </c>
     </row>
     <row r="114" spans="1:14">
@@ -8456,14 +8564,35 @@
       <c r="D114" t="s">
         <v>394</v>
       </c>
+      <c r="E114" t="s">
+        <v>403</v>
+      </c>
+      <c r="F114" t="s">
+        <v>437</v>
+      </c>
+      <c r="G114" t="s">
+        <v>520</v>
+      </c>
+      <c r="H114" t="s">
+        <v>653</v>
+      </c>
+      <c r="I114" t="s">
+        <v>831</v>
+      </c>
+      <c r="J114" t="s">
+        <v>916</v>
+      </c>
       <c r="K114" t="s">
-        <v>899</v>
+        <v>919</v>
       </c>
       <c r="L114" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M114" t="s">
-        <v>899</v>
+        <v>921</v>
+      </c>
+      <c r="N114" t="s">
+        <v>1010</v>
       </c>
     </row>
     <row r="115" spans="1:14">
@@ -8479,14 +8608,35 @@
       <c r="D115" t="s">
         <v>394</v>
       </c>
+      <c r="E115" t="s">
+        <v>403</v>
+      </c>
+      <c r="F115" t="s">
+        <v>435</v>
+      </c>
+      <c r="G115" t="s">
+        <v>518</v>
+      </c>
+      <c r="H115" t="s">
+        <v>654</v>
+      </c>
+      <c r="I115" t="s">
+        <v>832</v>
+      </c>
+      <c r="J115" t="s">
+        <v>916</v>
+      </c>
       <c r="K115" t="s">
-        <v>899</v>
+        <v>919</v>
       </c>
       <c r="L115" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M115" t="s">
-        <v>899</v>
+        <v>921</v>
+      </c>
+      <c r="N115" t="s">
+        <v>1011</v>
       </c>
     </row>
     <row r="116" spans="1:14">
@@ -8502,14 +8652,35 @@
       <c r="D116" t="s">
         <v>394</v>
       </c>
+      <c r="E116" t="s">
+        <v>403</v>
+      </c>
+      <c r="F116" t="s">
+        <v>433</v>
+      </c>
+      <c r="G116" t="s">
+        <v>521</v>
+      </c>
+      <c r="H116" t="s">
+        <v>655</v>
+      </c>
+      <c r="I116" t="s">
+        <v>833</v>
+      </c>
+      <c r="J116" t="s">
+        <v>916</v>
+      </c>
       <c r="K116" t="s">
-        <v>899</v>
+        <v>919</v>
       </c>
       <c r="L116" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M116" t="s">
-        <v>899</v>
+        <v>921</v>
+      </c>
+      <c r="N116" t="s">
+        <v>1012</v>
       </c>
     </row>
     <row r="117" spans="1:14">
@@ -8525,14 +8696,35 @@
       <c r="D117" t="s">
         <v>395</v>
       </c>
+      <c r="E117" t="s">
+        <v>403</v>
+      </c>
+      <c r="F117" t="s">
+        <v>437</v>
+      </c>
+      <c r="G117" t="s">
+        <v>520</v>
+      </c>
+      <c r="H117" t="s">
+        <v>650</v>
+      </c>
+      <c r="I117" t="s">
+        <v>834</v>
+      </c>
+      <c r="J117" t="s">
+        <v>917</v>
+      </c>
       <c r="K117" t="s">
-        <v>899</v>
+        <v>919</v>
       </c>
       <c r="L117" t="b">
         <v>1</v>
       </c>
       <c r="M117" t="s">
-        <v>899</v>
+        <v>922</v>
+      </c>
+      <c r="N117" t="s">
+        <v>1007</v>
       </c>
     </row>
     <row r="118" spans="1:14">
@@ -8548,14 +8740,35 @@
       <c r="D118" t="s">
         <v>392</v>
       </c>
+      <c r="E118" t="s">
+        <v>403</v>
+      </c>
+      <c r="F118" t="s">
+        <v>436</v>
+      </c>
+      <c r="G118" t="s">
+        <v>523</v>
+      </c>
+      <c r="H118" t="s">
+        <v>656</v>
+      </c>
+      <c r="I118" t="s">
+        <v>835</v>
+      </c>
+      <c r="J118" t="s">
+        <v>916</v>
+      </c>
       <c r="K118" t="s">
-        <v>899</v>
+        <v>919</v>
       </c>
       <c r="L118" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M118" t="s">
-        <v>899</v>
+        <v>921</v>
+      </c>
+      <c r="N118" t="s">
+        <v>1013</v>
       </c>
     </row>
     <row r="119" spans="1:14">
@@ -8571,14 +8784,35 @@
       <c r="D119" t="s">
         <v>393</v>
       </c>
+      <c r="E119" t="s">
+        <v>403</v>
+      </c>
+      <c r="F119" t="s">
+        <v>435</v>
+      </c>
+      <c r="G119" t="s">
+        <v>518</v>
+      </c>
+      <c r="H119" t="s">
+        <v>654</v>
+      </c>
+      <c r="I119" t="s">
+        <v>836</v>
+      </c>
+      <c r="J119" t="s">
+        <v>917</v>
+      </c>
       <c r="K119" t="s">
-        <v>899</v>
+        <v>919</v>
       </c>
       <c r="L119" t="b">
         <v>1</v>
       </c>
       <c r="M119" t="s">
-        <v>899</v>
+        <v>922</v>
+      </c>
+      <c r="N119" t="s">
+        <v>1011</v>
       </c>
     </row>
     <row r="120" spans="1:14">
@@ -8594,14 +8828,35 @@
       <c r="D120" t="s">
         <v>392</v>
       </c>
+      <c r="E120" t="s">
+        <v>403</v>
+      </c>
+      <c r="F120" t="s">
+        <v>438</v>
+      </c>
+      <c r="G120" t="s">
+        <v>524</v>
+      </c>
+      <c r="H120" t="s">
+        <v>657</v>
+      </c>
+      <c r="I120" t="s">
+        <v>837</v>
+      </c>
+      <c r="J120" t="s">
+        <v>916</v>
+      </c>
       <c r="K120" t="s">
-        <v>899</v>
+        <v>919</v>
       </c>
       <c r="L120" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M120" t="s">
-        <v>899</v>
+        <v>921</v>
+      </c>
+      <c r="N120" t="s">
+        <v>1014</v>
       </c>
     </row>
     <row r="121" spans="1:14">
@@ -8617,14 +8872,35 @@
       <c r="D121" t="s">
         <v>393</v>
       </c>
+      <c r="E121" t="s">
+        <v>403</v>
+      </c>
+      <c r="F121" t="s">
+        <v>436</v>
+      </c>
+      <c r="G121" t="s">
+        <v>519</v>
+      </c>
+      <c r="H121" t="s">
+        <v>658</v>
+      </c>
+      <c r="I121" t="s">
+        <v>838</v>
+      </c>
+      <c r="J121" t="s">
+        <v>916</v>
+      </c>
       <c r="K121" t="s">
-        <v>899</v>
+        <v>919</v>
       </c>
       <c r="L121" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M121" t="s">
-        <v>899</v>
+        <v>921</v>
+      </c>
+      <c r="N121" t="s">
+        <v>1015</v>
       </c>
     </row>
     <row r="122" spans="1:14">
@@ -8640,14 +8916,35 @@
       <c r="D122" t="s">
         <v>394</v>
       </c>
+      <c r="E122" t="s">
+        <v>401</v>
+      </c>
+      <c r="F122" t="s">
+        <v>439</v>
+      </c>
+      <c r="G122" t="s">
+        <v>525</v>
+      </c>
+      <c r="H122" t="s">
+        <v>659</v>
+      </c>
+      <c r="I122" t="s">
+        <v>839</v>
+      </c>
+      <c r="J122" t="s">
+        <v>916</v>
+      </c>
       <c r="K122" t="s">
-        <v>899</v>
+        <v>919</v>
       </c>
       <c r="L122" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M122" t="s">
-        <v>899</v>
+        <v>921</v>
+      </c>
+      <c r="N122" t="s">
+        <v>1016</v>
       </c>
     </row>
     <row r="123" spans="1:14">
@@ -8670,28 +8967,28 @@
         <v>431</v>
       </c>
       <c r="G123" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="H123" t="s">
-        <v>648</v>
+        <v>660</v>
       </c>
       <c r="I123" t="s">
-        <v>818</v>
+        <v>840</v>
       </c>
       <c r="J123" t="s">
-        <v>894</v>
+        <v>916</v>
       </c>
       <c r="K123" t="s">
-        <v>897</v>
+        <v>919</v>
       </c>
       <c r="L123" t="b">
         <v>0</v>
       </c>
       <c r="M123" t="s">
-        <v>900</v>
+        <v>921</v>
       </c>
       <c r="N123" t="s">
-        <v>988</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="124" spans="1:14">
@@ -8711,31 +9008,31 @@
         <v>404</v>
       </c>
       <c r="F124" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="G124" t="s">
-        <v>521</v>
+        <v>526</v>
       </c>
       <c r="H124" t="s">
-        <v>649</v>
+        <v>661</v>
       </c>
       <c r="I124" t="s">
-        <v>819</v>
+        <v>841</v>
       </c>
       <c r="J124" t="s">
-        <v>894</v>
+        <v>916</v>
       </c>
       <c r="K124" t="s">
-        <v>897</v>
+        <v>919</v>
       </c>
       <c r="L124" t="b">
         <v>0</v>
       </c>
       <c r="M124" t="s">
-        <v>900</v>
+        <v>921</v>
       </c>
       <c r="N124" t="s">
-        <v>989</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="125" spans="1:14">
@@ -8755,31 +9052,31 @@
         <v>404</v>
       </c>
       <c r="F125" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="G125" t="s">
-        <v>521</v>
+        <v>526</v>
       </c>
       <c r="H125" t="s">
-        <v>650</v>
+        <v>662</v>
       </c>
       <c r="I125" t="s">
-        <v>820</v>
+        <v>842</v>
       </c>
       <c r="J125" t="s">
-        <v>894</v>
+        <v>916</v>
       </c>
       <c r="K125" t="s">
-        <v>897</v>
+        <v>919</v>
       </c>
       <c r="L125" t="b">
         <v>0</v>
       </c>
       <c r="M125" t="s">
-        <v>900</v>
+        <v>921</v>
       </c>
       <c r="N125" t="s">
-        <v>990</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="126" spans="1:14">
@@ -8799,31 +9096,31 @@
         <v>404</v>
       </c>
       <c r="F126" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="G126" t="s">
-        <v>522</v>
+        <v>527</v>
       </c>
       <c r="H126" t="s">
-        <v>651</v>
+        <v>663</v>
       </c>
       <c r="I126" t="s">
-        <v>821</v>
+        <v>843</v>
       </c>
       <c r="J126" t="s">
-        <v>894</v>
+        <v>916</v>
       </c>
       <c r="K126" t="s">
-        <v>897</v>
+        <v>919</v>
       </c>
       <c r="L126" t="b">
         <v>0</v>
       </c>
       <c r="M126" t="s">
-        <v>900</v>
+        <v>921</v>
       </c>
       <c r="N126" t="s">
-        <v>991</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="127" spans="1:14">
@@ -8843,31 +9140,31 @@
         <v>404</v>
       </c>
       <c r="F127" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="G127" t="s">
-        <v>522</v>
+        <v>527</v>
       </c>
       <c r="H127" t="s">
-        <v>652</v>
+        <v>664</v>
       </c>
       <c r="I127" t="s">
-        <v>822</v>
+        <v>844</v>
       </c>
       <c r="J127" t="s">
-        <v>894</v>
+        <v>916</v>
       </c>
       <c r="K127" t="s">
-        <v>897</v>
+        <v>919</v>
       </c>
       <c r="L127" t="b">
         <v>0</v>
       </c>
       <c r="M127" t="s">
-        <v>900</v>
+        <v>921</v>
       </c>
       <c r="N127" t="s">
-        <v>992</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="128" spans="1:14">
@@ -8887,31 +9184,31 @@
         <v>404</v>
       </c>
       <c r="F128" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="G128" t="s">
-        <v>523</v>
+        <v>528</v>
       </c>
       <c r="H128" t="s">
-        <v>653</v>
+        <v>665</v>
       </c>
       <c r="I128" t="s">
-        <v>823</v>
+        <v>845</v>
       </c>
       <c r="J128" t="s">
-        <v>894</v>
+        <v>916</v>
       </c>
       <c r="K128" t="s">
-        <v>897</v>
+        <v>919</v>
       </c>
       <c r="L128" t="b">
         <v>0</v>
       </c>
       <c r="M128" t="s">
-        <v>900</v>
+        <v>921</v>
       </c>
       <c r="N128" t="s">
-        <v>993</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="129" spans="1:14">
@@ -8931,31 +9228,31 @@
         <v>404</v>
       </c>
       <c r="F129" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="G129" t="s">
-        <v>524</v>
+        <v>529</v>
       </c>
       <c r="H129" t="s">
-        <v>654</v>
+        <v>666</v>
       </c>
       <c r="I129" t="s">
-        <v>824</v>
+        <v>846</v>
       </c>
       <c r="J129" t="s">
-        <v>894</v>
+        <v>916</v>
       </c>
       <c r="K129" t="s">
-        <v>897</v>
+        <v>919</v>
       </c>
       <c r="L129" t="b">
         <v>0</v>
       </c>
       <c r="M129" t="s">
-        <v>900</v>
+        <v>921</v>
       </c>
       <c r="N129" t="s">
-        <v>994</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="130" spans="1:14">
@@ -8975,31 +9272,31 @@
         <v>404</v>
       </c>
       <c r="F130" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="G130" t="s">
-        <v>525</v>
+        <v>530</v>
       </c>
       <c r="H130" t="s">
-        <v>655</v>
+        <v>667</v>
       </c>
       <c r="I130" t="s">
-        <v>825</v>
+        <v>847</v>
       </c>
       <c r="J130" t="s">
-        <v>894</v>
+        <v>916</v>
       </c>
       <c r="K130" t="s">
-        <v>897</v>
+        <v>919</v>
       </c>
       <c r="L130" t="b">
         <v>0</v>
       </c>
       <c r="M130" t="s">
-        <v>900</v>
+        <v>921</v>
       </c>
       <c r="N130" t="s">
-        <v>995</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="131" spans="1:14">
@@ -9019,31 +9316,31 @@
         <v>404</v>
       </c>
       <c r="F131" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="G131" t="s">
-        <v>526</v>
+        <v>531</v>
       </c>
       <c r="H131" t="s">
-        <v>656</v>
+        <v>668</v>
       </c>
       <c r="I131" t="s">
-        <v>826</v>
+        <v>848</v>
       </c>
       <c r="J131" t="s">
-        <v>894</v>
+        <v>916</v>
       </c>
       <c r="K131" t="s">
-        <v>897</v>
+        <v>919</v>
       </c>
       <c r="L131" t="b">
         <v>0</v>
       </c>
       <c r="M131" t="s">
-        <v>900</v>
+        <v>921</v>
       </c>
       <c r="N131" t="s">
-        <v>996</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="132" spans="1:14">
@@ -9063,31 +9360,31 @@
         <v>404</v>
       </c>
       <c r="F132" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="G132" t="s">
-        <v>522</v>
+        <v>527</v>
       </c>
       <c r="H132" t="s">
-        <v>657</v>
+        <v>669</v>
       </c>
       <c r="I132" t="s">
-        <v>827</v>
+        <v>849</v>
       </c>
       <c r="J132" t="s">
-        <v>895</v>
+        <v>917</v>
       </c>
       <c r="K132" t="s">
-        <v>898</v>
+        <v>920</v>
       </c>
       <c r="L132" t="b">
         <v>1</v>
       </c>
       <c r="M132" t="s">
-        <v>901</v>
+        <v>922</v>
       </c>
       <c r="N132" t="s">
-        <v>997</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="133" spans="1:14">
@@ -9107,31 +9404,31 @@
         <v>404</v>
       </c>
       <c r="F133" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="G133" t="s">
-        <v>527</v>
+        <v>532</v>
       </c>
       <c r="H133" t="s">
-        <v>658</v>
+        <v>670</v>
       </c>
       <c r="I133" t="s">
-        <v>828</v>
+        <v>850</v>
       </c>
       <c r="J133" t="s">
-        <v>894</v>
+        <v>916</v>
       </c>
       <c r="K133" t="s">
-        <v>898</v>
+        <v>920</v>
       </c>
       <c r="L133" t="b">
         <v>1</v>
       </c>
       <c r="M133" t="s">
-        <v>901</v>
+        <v>922</v>
       </c>
       <c r="N133" t="s">
-        <v>998</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="134" spans="1:14">
@@ -9151,31 +9448,31 @@
         <v>404</v>
       </c>
       <c r="F134" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="G134" t="s">
-        <v>528</v>
+        <v>533</v>
       </c>
       <c r="H134" t="s">
-        <v>659</v>
+        <v>671</v>
       </c>
       <c r="I134" t="s">
-        <v>829</v>
+        <v>851</v>
       </c>
       <c r="J134" t="s">
-        <v>894</v>
+        <v>916</v>
       </c>
       <c r="K134" t="s">
-        <v>897</v>
+        <v>919</v>
       </c>
       <c r="L134" t="b">
         <v>0</v>
       </c>
       <c r="M134" t="s">
-        <v>900</v>
+        <v>921</v>
       </c>
       <c r="N134" t="s">
-        <v>999</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="135" spans="1:14">
@@ -9195,31 +9492,31 @@
         <v>404</v>
       </c>
       <c r="F135" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="G135" t="s">
-        <v>528</v>
+        <v>533</v>
       </c>
       <c r="H135" t="s">
-        <v>659</v>
+        <v>671</v>
       </c>
       <c r="I135" t="s">
-        <v>830</v>
+        <v>852</v>
       </c>
       <c r="J135" t="s">
-        <v>894</v>
+        <v>916</v>
       </c>
       <c r="K135" t="s">
-        <v>897</v>
+        <v>919</v>
       </c>
       <c r="L135" t="b">
         <v>0</v>
       </c>
       <c r="M135" t="s">
-        <v>900</v>
+        <v>921</v>
       </c>
       <c r="N135" t="s">
-        <v>999</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="136" spans="1:14">
@@ -9239,31 +9536,31 @@
         <v>405</v>
       </c>
       <c r="F136" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="G136" t="s">
-        <v>529</v>
+        <v>534</v>
       </c>
       <c r="H136" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="I136" t="s">
-        <v>831</v>
+        <v>853</v>
       </c>
       <c r="J136" t="s">
-        <v>895</v>
+        <v>917</v>
       </c>
       <c r="K136" t="s">
-        <v>898</v>
+        <v>920</v>
       </c>
       <c r="L136" t="b">
         <v>1</v>
       </c>
       <c r="M136" t="s">
-        <v>901</v>
+        <v>922</v>
       </c>
       <c r="N136" t="s">
-        <v>1000</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="137" spans="1:14">
@@ -9283,31 +9580,31 @@
         <v>405</v>
       </c>
       <c r="F137" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="G137" t="s">
-        <v>530</v>
+        <v>535</v>
       </c>
       <c r="H137" t="s">
-        <v>661</v>
+        <v>673</v>
       </c>
       <c r="I137" t="s">
-        <v>832</v>
+        <v>854</v>
       </c>
       <c r="J137" t="s">
-        <v>894</v>
+        <v>916</v>
       </c>
       <c r="K137" t="s">
-        <v>897</v>
+        <v>919</v>
       </c>
       <c r="L137" t="b">
         <v>0</v>
       </c>
       <c r="M137" t="s">
-        <v>900</v>
+        <v>921</v>
       </c>
       <c r="N137" t="s">
-        <v>1001</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="138" spans="1:14">
@@ -9327,31 +9624,31 @@
         <v>405</v>
       </c>
       <c r="F138" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="G138" t="s">
-        <v>531</v>
+        <v>536</v>
       </c>
       <c r="H138" t="s">
-        <v>662</v>
+        <v>674</v>
       </c>
       <c r="I138" t="s">
-        <v>833</v>
+        <v>855</v>
       </c>
       <c r="J138" t="s">
-        <v>894</v>
+        <v>916</v>
       </c>
       <c r="K138" t="s">
-        <v>897</v>
+        <v>919</v>
       </c>
       <c r="L138" t="b">
         <v>0</v>
       </c>
       <c r="M138" t="s">
-        <v>900</v>
+        <v>921</v>
       </c>
       <c r="N138" t="s">
-        <v>1002</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="139" spans="1:14">
@@ -9371,31 +9668,31 @@
         <v>405</v>
       </c>
       <c r="F139" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="G139" t="s">
-        <v>532</v>
+        <v>537</v>
       </c>
       <c r="H139" t="s">
-        <v>663</v>
+        <v>675</v>
       </c>
       <c r="I139" t="s">
-        <v>834</v>
+        <v>856</v>
       </c>
       <c r="J139" t="s">
-        <v>894</v>
+        <v>916</v>
       </c>
       <c r="K139" t="s">
-        <v>897</v>
+        <v>919</v>
       </c>
       <c r="L139" t="b">
         <v>0</v>
       </c>
       <c r="M139" t="s">
-        <v>900</v>
+        <v>921</v>
       </c>
       <c r="N139" t="s">
-        <v>1003</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="140" spans="1:14">
@@ -9415,31 +9712,31 @@
         <v>405</v>
       </c>
       <c r="F140" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="G140" t="s">
-        <v>533</v>
+        <v>538</v>
       </c>
       <c r="H140" t="s">
-        <v>664</v>
+        <v>676</v>
       </c>
       <c r="I140" t="s">
-        <v>835</v>
+        <v>857</v>
       </c>
       <c r="J140" t="s">
-        <v>894</v>
+        <v>916</v>
       </c>
       <c r="K140" t="s">
-        <v>897</v>
+        <v>919</v>
       </c>
       <c r="L140" t="b">
         <v>0</v>
       </c>
       <c r="M140" t="s">
-        <v>900</v>
+        <v>921</v>
       </c>
       <c r="N140" t="s">
-        <v>1004</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="141" spans="1:14">
@@ -9459,31 +9756,31 @@
         <v>405</v>
       </c>
       <c r="F141" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="G141" t="s">
-        <v>534</v>
+        <v>539</v>
       </c>
       <c r="H141" t="s">
-        <v>665</v>
+        <v>677</v>
       </c>
       <c r="I141" t="s">
-        <v>836</v>
+        <v>858</v>
       </c>
       <c r="J141" t="s">
-        <v>894</v>
+        <v>916</v>
       </c>
       <c r="K141" t="s">
-        <v>897</v>
+        <v>919</v>
       </c>
       <c r="L141" t="b">
         <v>0</v>
       </c>
       <c r="M141" t="s">
-        <v>900</v>
+        <v>921</v>
       </c>
       <c r="N141" t="s">
-        <v>1005</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="142" spans="1:14">
@@ -9503,31 +9800,31 @@
         <v>405</v>
       </c>
       <c r="F142" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="G142" t="s">
-        <v>535</v>
+        <v>540</v>
       </c>
       <c r="H142" t="s">
-        <v>666</v>
+        <v>678</v>
       </c>
       <c r="I142" t="s">
-        <v>837</v>
+        <v>859</v>
       </c>
       <c r="J142" t="s">
-        <v>894</v>
+        <v>916</v>
       </c>
       <c r="K142" t="s">
-        <v>897</v>
+        <v>919</v>
       </c>
       <c r="L142" t="b">
         <v>0</v>
       </c>
       <c r="M142" t="s">
-        <v>900</v>
+        <v>921</v>
       </c>
       <c r="N142" t="s">
-        <v>1006</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="143" spans="1:14">
@@ -9547,31 +9844,31 @@
         <v>405</v>
       </c>
       <c r="F143" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="G143" t="s">
-        <v>532</v>
+        <v>537</v>
       </c>
       <c r="H143" t="s">
-        <v>663</v>
+        <v>675</v>
       </c>
       <c r="I143" t="s">
-        <v>838</v>
+        <v>860</v>
       </c>
       <c r="J143" t="s">
-        <v>894</v>
+        <v>916</v>
       </c>
       <c r="K143" t="s">
-        <v>897</v>
+        <v>919</v>
       </c>
       <c r="L143" t="b">
         <v>0</v>
       </c>
       <c r="M143" t="s">
-        <v>900</v>
+        <v>921</v>
       </c>
       <c r="N143" t="s">
-        <v>1003</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="144" spans="1:14">
@@ -9591,31 +9888,31 @@
         <v>405</v>
       </c>
       <c r="F144" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="G144" t="s">
-        <v>530</v>
+        <v>535</v>
       </c>
       <c r="H144" t="s">
-        <v>667</v>
+        <v>679</v>
       </c>
       <c r="I144" t="s">
-        <v>839</v>
+        <v>861</v>
       </c>
       <c r="J144" t="s">
-        <v>894</v>
+        <v>916</v>
       </c>
       <c r="K144" t="s">
-        <v>897</v>
+        <v>919</v>
       </c>
       <c r="L144" t="b">
         <v>0</v>
       </c>
       <c r="M144" t="s">
-        <v>900</v>
+        <v>921</v>
       </c>
       <c r="N144" t="s">
-        <v>1007</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="145" spans="1:14">
@@ -9635,31 +9932,31 @@
         <v>405</v>
       </c>
       <c r="F145" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="G145" t="s">
-        <v>536</v>
+        <v>541</v>
       </c>
       <c r="H145" t="s">
-        <v>668</v>
+        <v>680</v>
       </c>
       <c r="I145" t="s">
-        <v>840</v>
+        <v>862</v>
       </c>
       <c r="J145" t="s">
-        <v>894</v>
+        <v>916</v>
       </c>
       <c r="K145" t="s">
-        <v>897</v>
+        <v>919</v>
       </c>
       <c r="L145" t="b">
         <v>0</v>
       </c>
       <c r="M145" t="s">
-        <v>900</v>
+        <v>921</v>
       </c>
       <c r="N145" t="s">
-        <v>1008</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="146" spans="1:14">
@@ -9679,31 +9976,31 @@
         <v>405</v>
       </c>
       <c r="F146" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="G146" t="s">
-        <v>537</v>
+        <v>542</v>
       </c>
       <c r="H146" t="s">
-        <v>669</v>
+        <v>681</v>
       </c>
       <c r="I146" t="s">
-        <v>841</v>
+        <v>863</v>
       </c>
       <c r="J146" t="s">
-        <v>894</v>
+        <v>916</v>
       </c>
       <c r="K146" t="s">
-        <v>897</v>
+        <v>919</v>
       </c>
       <c r="L146" t="b">
         <v>0</v>
       </c>
       <c r="M146" t="s">
-        <v>900</v>
+        <v>921</v>
       </c>
       <c r="N146" t="s">
-        <v>1009</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="147" spans="1:14">
@@ -9726,28 +10023,28 @@
         <v>410</v>
       </c>
       <c r="G147" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="H147" t="s">
-        <v>568</v>
+        <v>572</v>
       </c>
       <c r="I147" t="s">
-        <v>842</v>
+        <v>864</v>
       </c>
       <c r="J147" t="s">
-        <v>894</v>
+        <v>916</v>
       </c>
       <c r="K147" t="s">
-        <v>897</v>
+        <v>919</v>
       </c>
       <c r="L147" t="b">
         <v>0</v>
       </c>
       <c r="M147" t="s">
-        <v>900</v>
+        <v>921</v>
       </c>
       <c r="N147" t="s">
-        <v>908</v>
+        <v>929</v>
       </c>
     </row>
     <row r="148" spans="1:14">
@@ -9770,28 +10067,28 @@
         <v>425</v>
       </c>
       <c r="G148" t="s">
-        <v>538</v>
+        <v>543</v>
       </c>
       <c r="H148" t="s">
-        <v>670</v>
+        <v>682</v>
       </c>
       <c r="I148" t="s">
-        <v>843</v>
+        <v>865</v>
       </c>
       <c r="J148" t="s">
-        <v>895</v>
+        <v>917</v>
       </c>
       <c r="K148" t="s">
-        <v>897</v>
+        <v>919</v>
       </c>
       <c r="L148" t="b">
         <v>1</v>
       </c>
       <c r="M148" t="s">
-        <v>901</v>
+        <v>922</v>
       </c>
       <c r="N148" t="s">
-        <v>1010</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="149" spans="1:14">
@@ -9811,31 +10108,31 @@
         <v>405</v>
       </c>
       <c r="F149" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="G149" t="s">
-        <v>535</v>
+        <v>540</v>
       </c>
       <c r="H149" t="s">
-        <v>671</v>
+        <v>683</v>
       </c>
       <c r="I149" t="s">
-        <v>844</v>
+        <v>866</v>
       </c>
       <c r="J149" t="s">
-        <v>894</v>
+        <v>916</v>
       </c>
       <c r="K149" t="s">
-        <v>897</v>
+        <v>919</v>
       </c>
       <c r="L149" t="b">
         <v>0</v>
       </c>
       <c r="M149" t="s">
-        <v>900</v>
+        <v>921</v>
       </c>
       <c r="N149" t="s">
-        <v>1011</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="150" spans="1:14">
@@ -9855,31 +10152,31 @@
         <v>405</v>
       </c>
       <c r="F150" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="G150" t="s">
-        <v>530</v>
+        <v>535</v>
       </c>
       <c r="H150" t="s">
-        <v>661</v>
+        <v>673</v>
       </c>
       <c r="I150" t="s">
-        <v>845</v>
+        <v>867</v>
       </c>
       <c r="J150" t="s">
-        <v>895</v>
+        <v>917</v>
       </c>
       <c r="K150" t="s">
-        <v>897</v>
+        <v>919</v>
       </c>
       <c r="L150" t="b">
         <v>1</v>
       </c>
       <c r="M150" t="s">
-        <v>901</v>
+        <v>922</v>
       </c>
       <c r="N150" t="s">
-        <v>1001</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="151" spans="1:14">
@@ -9902,28 +10199,28 @@
         <v>430</v>
       </c>
       <c r="G151" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="H151" t="s">
-        <v>672</v>
+        <v>684</v>
       </c>
       <c r="I151" t="s">
-        <v>846</v>
+        <v>868</v>
       </c>
       <c r="J151" t="s">
-        <v>895</v>
+        <v>917</v>
       </c>
       <c r="K151" t="s">
-        <v>897</v>
+        <v>919</v>
       </c>
       <c r="L151" t="b">
         <v>1</v>
       </c>
       <c r="M151" t="s">
-        <v>901</v>
+        <v>922</v>
       </c>
       <c r="N151" t="s">
-        <v>1012</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="152" spans="1:14">
@@ -9943,31 +10240,31 @@
         <v>405</v>
       </c>
       <c r="F152" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="G152" t="s">
-        <v>536</v>
+        <v>541</v>
       </c>
       <c r="H152" t="s">
-        <v>668</v>
+        <v>680</v>
       </c>
       <c r="I152" t="s">
-        <v>847</v>
+        <v>869</v>
       </c>
       <c r="J152" t="s">
-        <v>894</v>
+        <v>916</v>
       </c>
       <c r="K152" t="s">
-        <v>897</v>
+        <v>919</v>
       </c>
       <c r="L152" t="b">
         <v>0</v>
       </c>
       <c r="M152" t="s">
-        <v>900</v>
+        <v>921</v>
       </c>
       <c r="N152" t="s">
-        <v>1008</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="153" spans="1:14">
@@ -9987,31 +10284,31 @@
         <v>397</v>
       </c>
       <c r="F153" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="G153" t="s">
-        <v>539</v>
+        <v>544</v>
       </c>
       <c r="H153" t="s">
-        <v>673</v>
+        <v>685</v>
       </c>
       <c r="I153" t="s">
-        <v>848</v>
+        <v>870</v>
       </c>
       <c r="J153" t="s">
-        <v>895</v>
+        <v>917</v>
       </c>
       <c r="K153" t="s">
-        <v>897</v>
+        <v>919</v>
       </c>
       <c r="L153" t="b">
         <v>1</v>
       </c>
       <c r="M153" t="s">
-        <v>901</v>
+        <v>922</v>
       </c>
       <c r="N153" t="s">
-        <v>1013</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="154" spans="1:14">
@@ -10031,31 +10328,31 @@
         <v>405</v>
       </c>
       <c r="F154" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="G154" t="s">
-        <v>530</v>
+        <v>535</v>
       </c>
       <c r="H154" t="s">
-        <v>674</v>
+        <v>686</v>
       </c>
       <c r="I154" t="s">
-        <v>849</v>
+        <v>871</v>
       </c>
       <c r="J154" t="s">
-        <v>894</v>
+        <v>916</v>
       </c>
       <c r="K154" t="s">
-        <v>897</v>
+        <v>919</v>
       </c>
       <c r="L154" t="b">
         <v>0</v>
       </c>
       <c r="M154" t="s">
-        <v>900</v>
+        <v>921</v>
       </c>
       <c r="N154" t="s">
-        <v>1014</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="155" spans="1:14">
@@ -10075,31 +10372,31 @@
         <v>399</v>
       </c>
       <c r="F155" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="G155" t="s">
-        <v>540</v>
+        <v>545</v>
       </c>
       <c r="H155" t="s">
-        <v>675</v>
+        <v>687</v>
       </c>
       <c r="I155" t="s">
-        <v>850</v>
+        <v>872</v>
       </c>
       <c r="J155" t="s">
-        <v>894</v>
+        <v>916</v>
       </c>
       <c r="K155" t="s">
-        <v>897</v>
+        <v>919</v>
       </c>
       <c r="L155" t="b">
         <v>0</v>
       </c>
       <c r="M155" t="s">
-        <v>900</v>
+        <v>921</v>
       </c>
       <c r="N155" t="s">
-        <v>1015</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="156" spans="1:14">
@@ -10119,31 +10416,31 @@
         <v>399</v>
       </c>
       <c r="F156" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="G156" t="s">
-        <v>541</v>
+        <v>546</v>
       </c>
       <c r="H156" t="s">
-        <v>676</v>
+        <v>688</v>
       </c>
       <c r="I156" t="s">
-        <v>851</v>
+        <v>873</v>
       </c>
       <c r="J156" t="s">
-        <v>894</v>
+        <v>916</v>
       </c>
       <c r="K156" t="s">
-        <v>897</v>
+        <v>919</v>
       </c>
       <c r="L156" t="b">
         <v>0</v>
       </c>
       <c r="M156" t="s">
-        <v>900</v>
+        <v>921</v>
       </c>
       <c r="N156" t="s">
-        <v>1016</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="157" spans="1:14">
@@ -10163,31 +10460,31 @@
         <v>399</v>
       </c>
       <c r="F157" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="G157" t="s">
-        <v>542</v>
+        <v>547</v>
       </c>
       <c r="H157" t="s">
-        <v>677</v>
+        <v>689</v>
       </c>
       <c r="I157" t="s">
-        <v>852</v>
+        <v>874</v>
       </c>
       <c r="J157" t="s">
-        <v>894</v>
+        <v>916</v>
       </c>
       <c r="K157" t="s">
-        <v>897</v>
+        <v>919</v>
       </c>
       <c r="L157" t="b">
         <v>0</v>
       </c>
       <c r="M157" t="s">
-        <v>900</v>
+        <v>921</v>
       </c>
       <c r="N157" t="s">
-        <v>1017</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="158" spans="1:14">
@@ -10207,31 +10504,31 @@
         <v>399</v>
       </c>
       <c r="F158" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="G158" t="s">
-        <v>543</v>
+        <v>548</v>
       </c>
       <c r="H158" t="s">
-        <v>678</v>
+        <v>690</v>
       </c>
       <c r="I158" t="s">
-        <v>853</v>
+        <v>875</v>
       </c>
       <c r="J158" t="s">
-        <v>894</v>
+        <v>916</v>
       </c>
       <c r="K158" t="s">
-        <v>897</v>
+        <v>919</v>
       </c>
       <c r="L158" t="b">
         <v>0</v>
       </c>
       <c r="M158" t="s">
-        <v>900</v>
+        <v>921</v>
       </c>
       <c r="N158" t="s">
-        <v>1018</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="159" spans="1:14">
@@ -10251,31 +10548,31 @@
         <v>399</v>
       </c>
       <c r="F159" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="G159" t="s">
-        <v>541</v>
+        <v>546</v>
       </c>
       <c r="H159" t="s">
-        <v>679</v>
+        <v>691</v>
       </c>
       <c r="I159" t="s">
-        <v>854</v>
+        <v>876</v>
       </c>
       <c r="J159" t="s">
-        <v>894</v>
+        <v>916</v>
       </c>
       <c r="K159" t="s">
-        <v>897</v>
+        <v>919</v>
       </c>
       <c r="L159" t="b">
         <v>0</v>
       </c>
       <c r="M159" t="s">
-        <v>900</v>
+        <v>921</v>
       </c>
       <c r="N159" t="s">
-        <v>1019</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="160" spans="1:14">
@@ -10295,31 +10592,31 @@
         <v>399</v>
       </c>
       <c r="F160" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="G160" t="s">
-        <v>544</v>
+        <v>549</v>
       </c>
       <c r="H160" t="s">
-        <v>680</v>
+        <v>692</v>
       </c>
       <c r="I160" t="s">
-        <v>855</v>
+        <v>877</v>
       </c>
       <c r="J160" t="s">
-        <v>894</v>
+        <v>916</v>
       </c>
       <c r="K160" t="s">
-        <v>897</v>
+        <v>919</v>
       </c>
       <c r="L160" t="b">
         <v>0</v>
       </c>
       <c r="M160" t="s">
-        <v>900</v>
+        <v>921</v>
       </c>
       <c r="N160" t="s">
-        <v>1020</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="161" spans="1:14">
@@ -10342,28 +10639,28 @@
         <v>419</v>
       </c>
       <c r="G161" t="s">
-        <v>545</v>
+        <v>550</v>
       </c>
       <c r="H161" t="s">
-        <v>681</v>
+        <v>693</v>
       </c>
       <c r="I161" t="s">
-        <v>856</v>
+        <v>878</v>
       </c>
       <c r="J161" t="s">
-        <v>894</v>
+        <v>916</v>
       </c>
       <c r="K161" t="s">
-        <v>897</v>
+        <v>919</v>
       </c>
       <c r="L161" t="b">
         <v>0</v>
       </c>
       <c r="M161" t="s">
-        <v>900</v>
+        <v>921</v>
       </c>
       <c r="N161" t="s">
-        <v>1021</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="162" spans="1:14">
@@ -10386,28 +10683,28 @@
         <v>419</v>
       </c>
       <c r="G162" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H162" t="s">
-        <v>682</v>
+        <v>694</v>
       </c>
       <c r="I162" t="s">
-        <v>857</v>
+        <v>879</v>
       </c>
       <c r="J162" t="s">
-        <v>894</v>
+        <v>916</v>
       </c>
       <c r="K162" t="s">
-        <v>897</v>
+        <v>919</v>
       </c>
       <c r="L162" t="b">
         <v>0</v>
       </c>
       <c r="M162" t="s">
-        <v>900</v>
+        <v>921</v>
       </c>
       <c r="N162" t="s">
-        <v>1022</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="163" spans="1:14">
@@ -10430,28 +10727,28 @@
         <v>416</v>
       </c>
       <c r="G163" t="s">
-        <v>546</v>
+        <v>551</v>
       </c>
       <c r="H163" t="s">
-        <v>683</v>
+        <v>695</v>
       </c>
       <c r="I163" t="s">
-        <v>858</v>
+        <v>880</v>
       </c>
       <c r="J163" t="s">
-        <v>894</v>
+        <v>916</v>
       </c>
       <c r="K163" t="s">
-        <v>897</v>
+        <v>919</v>
       </c>
       <c r="L163" t="b">
         <v>0</v>
       </c>
       <c r="M163" t="s">
-        <v>900</v>
+        <v>921</v>
       </c>
       <c r="N163" t="s">
-        <v>1023</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="164" spans="1:14">
@@ -10474,28 +10771,28 @@
         <v>419</v>
       </c>
       <c r="G164" t="s">
-        <v>545</v>
+        <v>550</v>
       </c>
       <c r="H164" t="s">
-        <v>684</v>
+        <v>696</v>
       </c>
       <c r="I164" t="s">
-        <v>859</v>
+        <v>881</v>
       </c>
       <c r="J164" t="s">
-        <v>894</v>
+        <v>916</v>
       </c>
       <c r="K164" t="s">
-        <v>897</v>
+        <v>919</v>
       </c>
       <c r="L164" t="b">
         <v>0</v>
       </c>
       <c r="M164" t="s">
-        <v>900</v>
+        <v>921</v>
       </c>
       <c r="N164" t="s">
-        <v>1024</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="165" spans="1:14">
@@ -10518,28 +10815,28 @@
         <v>413</v>
       </c>
       <c r="G165" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H165" t="s">
-        <v>580</v>
+        <v>584</v>
       </c>
       <c r="I165" t="s">
-        <v>860</v>
+        <v>882</v>
       </c>
       <c r="J165" t="s">
-        <v>894</v>
+        <v>916</v>
       </c>
       <c r="K165" t="s">
-        <v>897</v>
+        <v>919</v>
       </c>
       <c r="L165" t="b">
         <v>0</v>
       </c>
       <c r="M165" t="s">
-        <v>900</v>
+        <v>921</v>
       </c>
       <c r="N165" t="s">
-        <v>920</v>
+        <v>941</v>
       </c>
     </row>
     <row r="166" spans="1:14">
@@ -10559,31 +10856,31 @@
         <v>399</v>
       </c>
       <c r="F166" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="G166" t="s">
-        <v>540</v>
+        <v>545</v>
       </c>
       <c r="H166" t="s">
-        <v>685</v>
+        <v>697</v>
       </c>
       <c r="I166" t="s">
-        <v>861</v>
+        <v>883</v>
       </c>
       <c r="J166" t="s">
-        <v>894</v>
+        <v>916</v>
       </c>
       <c r="K166" t="s">
-        <v>897</v>
+        <v>919</v>
       </c>
       <c r="L166" t="b">
         <v>0</v>
       </c>
       <c r="M166" t="s">
-        <v>900</v>
+        <v>921</v>
       </c>
       <c r="N166" t="s">
-        <v>1025</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="167" spans="1:14">
@@ -10603,31 +10900,31 @@
         <v>399</v>
       </c>
       <c r="F167" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="G167" t="s">
-        <v>541</v>
+        <v>546</v>
       </c>
       <c r="H167" t="s">
-        <v>676</v>
+        <v>688</v>
       </c>
       <c r="I167" t="s">
-        <v>862</v>
+        <v>884</v>
       </c>
       <c r="J167" t="s">
-        <v>894</v>
+        <v>916</v>
       </c>
       <c r="K167" t="s">
-        <v>897</v>
+        <v>919</v>
       </c>
       <c r="L167" t="b">
         <v>0</v>
       </c>
       <c r="M167" t="s">
-        <v>900</v>
+        <v>921</v>
       </c>
       <c r="N167" t="s">
-        <v>1016</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="168" spans="1:14">
@@ -10647,31 +10944,31 @@
         <v>399</v>
       </c>
       <c r="F168" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="G168" t="s">
-        <v>544</v>
+        <v>549</v>
       </c>
       <c r="H168" t="s">
-        <v>680</v>
+        <v>692</v>
       </c>
       <c r="I168" t="s">
-        <v>863</v>
+        <v>885</v>
       </c>
       <c r="J168" t="s">
-        <v>894</v>
+        <v>916</v>
       </c>
       <c r="K168" t="s">
-        <v>897</v>
+        <v>919</v>
       </c>
       <c r="L168" t="b">
         <v>0</v>
       </c>
       <c r="M168" t="s">
-        <v>900</v>
+        <v>921</v>
       </c>
       <c r="N168" t="s">
-        <v>1020</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="169" spans="1:14">
@@ -10691,31 +10988,31 @@
         <v>397</v>
       </c>
       <c r="F169" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="G169" t="s">
-        <v>547</v>
+        <v>552</v>
       </c>
       <c r="H169" t="s">
-        <v>686</v>
+        <v>698</v>
       </c>
       <c r="I169" t="s">
-        <v>864</v>
+        <v>886</v>
       </c>
       <c r="J169" t="s">
-        <v>894</v>
+        <v>916</v>
       </c>
       <c r="K169" t="s">
-        <v>897</v>
+        <v>919</v>
       </c>
       <c r="L169" t="b">
         <v>0</v>
       </c>
       <c r="M169" t="s">
-        <v>900</v>
+        <v>921</v>
       </c>
       <c r="N169" t="s">
-        <v>1026</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="170" spans="1:14">
@@ -10738,28 +11035,28 @@
         <v>426</v>
       </c>
       <c r="G170" t="s">
-        <v>548</v>
+        <v>553</v>
       </c>
       <c r="H170" t="s">
-        <v>687</v>
+        <v>699</v>
       </c>
       <c r="I170" t="s">
-        <v>865</v>
+        <v>887</v>
       </c>
       <c r="J170" t="s">
-        <v>894</v>
+        <v>916</v>
       </c>
       <c r="K170" t="s">
-        <v>897</v>
+        <v>919</v>
       </c>
       <c r="L170" t="b">
         <v>0</v>
       </c>
       <c r="M170" t="s">
-        <v>900</v>
+        <v>921</v>
       </c>
       <c r="N170" t="s">
-        <v>1027</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="171" spans="1:14">
@@ -10782,28 +11079,28 @@
         <v>413</v>
       </c>
       <c r="G171" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H171" t="s">
-        <v>580</v>
+        <v>584</v>
       </c>
       <c r="I171" t="s">
-        <v>866</v>
+        <v>888</v>
       </c>
       <c r="J171" t="s">
-        <v>894</v>
+        <v>916</v>
       </c>
       <c r="K171" t="s">
-        <v>897</v>
+        <v>919</v>
       </c>
       <c r="L171" t="b">
         <v>0</v>
       </c>
       <c r="M171" t="s">
-        <v>900</v>
+        <v>921</v>
       </c>
       <c r="N171" t="s">
-        <v>920</v>
+        <v>941</v>
       </c>
     </row>
     <row r="172" spans="1:14">
@@ -10823,31 +11120,31 @@
         <v>397</v>
       </c>
       <c r="F172" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="G172" t="s">
-        <v>539</v>
+        <v>544</v>
       </c>
       <c r="H172" t="s">
-        <v>688</v>
+        <v>700</v>
       </c>
       <c r="I172" t="s">
-        <v>867</v>
+        <v>889</v>
       </c>
       <c r="J172" t="s">
-        <v>896</v>
+        <v>918</v>
       </c>
       <c r="K172" t="s">
-        <v>898</v>
+        <v>920</v>
       </c>
       <c r="L172" t="b">
         <v>1</v>
       </c>
       <c r="M172" t="s">
-        <v>901</v>
+        <v>922</v>
       </c>
       <c r="N172" t="s">
-        <v>1028</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="173" spans="1:14">
@@ -10870,28 +11167,28 @@
         <v>413</v>
       </c>
       <c r="G173" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H173" t="s">
-        <v>580</v>
+        <v>584</v>
       </c>
       <c r="I173" t="s">
-        <v>868</v>
+        <v>890</v>
       </c>
       <c r="J173" t="s">
-        <v>894</v>
+        <v>916</v>
       </c>
       <c r="K173" t="s">
-        <v>897</v>
+        <v>919</v>
       </c>
       <c r="L173" t="b">
         <v>0</v>
       </c>
       <c r="M173" t="s">
-        <v>900</v>
+        <v>921</v>
       </c>
       <c r="N173" t="s">
-        <v>920</v>
+        <v>941</v>
       </c>
     </row>
     <row r="174" spans="1:14">
@@ -10914,28 +11211,28 @@
         <v>413</v>
       </c>
       <c r="G174" t="s">
-        <v>549</v>
+        <v>554</v>
       </c>
       <c r="H174" t="s">
-        <v>689</v>
+        <v>701</v>
       </c>
       <c r="I174" t="s">
-        <v>869</v>
+        <v>891</v>
       </c>
       <c r="J174" t="s">
-        <v>894</v>
+        <v>916</v>
       </c>
       <c r="K174" t="s">
-        <v>897</v>
+        <v>919</v>
       </c>
       <c r="L174" t="b">
         <v>0</v>
       </c>
       <c r="M174" t="s">
-        <v>900</v>
+        <v>921</v>
       </c>
       <c r="N174" t="s">
-        <v>1029</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="175" spans="1:14">
@@ -10958,28 +11255,28 @@
         <v>416</v>
       </c>
       <c r="G175" t="s">
-        <v>546</v>
+        <v>551</v>
       </c>
       <c r="H175" t="s">
-        <v>683</v>
+        <v>695</v>
       </c>
       <c r="I175" t="s">
-        <v>870</v>
+        <v>892</v>
       </c>
       <c r="J175" t="s">
-        <v>895</v>
+        <v>917</v>
       </c>
       <c r="K175" t="s">
-        <v>897</v>
+        <v>919</v>
       </c>
       <c r="L175" t="b">
         <v>1</v>
       </c>
       <c r="M175" t="s">
-        <v>901</v>
+        <v>922</v>
       </c>
       <c r="N175" t="s">
-        <v>1023</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="176" spans="1:14">
@@ -11002,28 +11299,28 @@
         <v>413</v>
       </c>
       <c r="G176" t="s">
-        <v>549</v>
+        <v>554</v>
       </c>
       <c r="H176" t="s">
-        <v>690</v>
+        <v>702</v>
       </c>
       <c r="I176" t="s">
-        <v>871</v>
+        <v>893</v>
       </c>
       <c r="J176" t="s">
-        <v>894</v>
+        <v>916</v>
       </c>
       <c r="K176" t="s">
-        <v>897</v>
+        <v>919</v>
       </c>
       <c r="L176" t="b">
         <v>0</v>
       </c>
       <c r="M176" t="s">
-        <v>900</v>
+        <v>921</v>
       </c>
       <c r="N176" t="s">
-        <v>1030</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="177" spans="1:14">
@@ -11043,31 +11340,31 @@
         <v>397</v>
       </c>
       <c r="F177" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="G177" t="s">
-        <v>550</v>
+        <v>555</v>
       </c>
       <c r="H177" t="s">
-        <v>691</v>
+        <v>703</v>
       </c>
       <c r="I177" t="s">
-        <v>872</v>
+        <v>894</v>
       </c>
       <c r="J177" t="s">
-        <v>894</v>
+        <v>916</v>
       </c>
       <c r="K177" t="s">
-        <v>897</v>
+        <v>919</v>
       </c>
       <c r="L177" t="b">
         <v>0</v>
       </c>
       <c r="M177" t="s">
-        <v>900</v>
+        <v>921</v>
       </c>
       <c r="N177" t="s">
-        <v>1031</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="178" spans="1:14">
@@ -11090,28 +11387,28 @@
         <v>420</v>
       </c>
       <c r="G178" t="s">
-        <v>551</v>
+        <v>556</v>
       </c>
       <c r="H178" t="s">
-        <v>692</v>
+        <v>704</v>
       </c>
       <c r="I178" t="s">
-        <v>873</v>
+        <v>895</v>
       </c>
       <c r="J178" t="s">
-        <v>895</v>
+        <v>917</v>
       </c>
       <c r="K178" t="s">
-        <v>898</v>
+        <v>920</v>
       </c>
       <c r="L178" t="b">
         <v>1</v>
       </c>
       <c r="M178" t="s">
-        <v>901</v>
+        <v>922</v>
       </c>
       <c r="N178" t="s">
-        <v>1032</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="179" spans="1:14">
@@ -11134,28 +11431,28 @@
         <v>413</v>
       </c>
       <c r="G179" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="H179" t="s">
-        <v>693</v>
+        <v>705</v>
       </c>
       <c r="I179" t="s">
-        <v>874</v>
+        <v>896</v>
       </c>
       <c r="J179" t="s">
-        <v>894</v>
+        <v>916</v>
       </c>
       <c r="K179" t="s">
-        <v>897</v>
+        <v>919</v>
       </c>
       <c r="L179" t="b">
         <v>0</v>
       </c>
       <c r="M179" t="s">
-        <v>900</v>
+        <v>921</v>
       </c>
       <c r="N179" t="s">
-        <v>1033</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="180" spans="1:14">
@@ -11178,28 +11475,28 @@
         <v>413</v>
       </c>
       <c r="G180" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="H180" t="s">
-        <v>575</v>
+        <v>579</v>
       </c>
       <c r="I180" t="s">
-        <v>875</v>
+        <v>897</v>
       </c>
       <c r="J180" t="s">
-        <v>894</v>
+        <v>916</v>
       </c>
       <c r="K180" t="s">
-        <v>897</v>
+        <v>919</v>
       </c>
       <c r="L180" t="b">
         <v>0</v>
       </c>
       <c r="M180" t="s">
-        <v>900</v>
+        <v>921</v>
       </c>
       <c r="N180" t="s">
-        <v>915</v>
+        <v>936</v>
       </c>
     </row>
     <row r="181" spans="1:14">
@@ -11222,28 +11519,28 @@
         <v>420</v>
       </c>
       <c r="G181" t="s">
-        <v>552</v>
+        <v>557</v>
       </c>
       <c r="H181" t="s">
-        <v>694</v>
+        <v>706</v>
       </c>
       <c r="I181" t="s">
-        <v>876</v>
+        <v>898</v>
       </c>
       <c r="J181" t="s">
-        <v>895</v>
+        <v>917</v>
       </c>
       <c r="K181" t="s">
-        <v>898</v>
+        <v>920</v>
       </c>
       <c r="L181" t="b">
         <v>1</v>
       </c>
       <c r="M181" t="s">
-        <v>901</v>
+        <v>922</v>
       </c>
       <c r="N181" t="s">
-        <v>1034</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="182" spans="1:14">
@@ -11266,28 +11563,28 @@
         <v>408</v>
       </c>
       <c r="G182" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="H182" t="s">
-        <v>563</v>
+        <v>567</v>
       </c>
       <c r="I182" t="s">
-        <v>877</v>
+        <v>899</v>
       </c>
       <c r="J182" t="s">
-        <v>896</v>
+        <v>918</v>
       </c>
       <c r="K182" t="s">
-        <v>898</v>
+        <v>920</v>
       </c>
       <c r="L182" t="b">
         <v>1</v>
       </c>
       <c r="M182" t="s">
-        <v>901</v>
+        <v>922</v>
       </c>
       <c r="N182" t="s">
-        <v>903</v>
+        <v>924</v>
       </c>
     </row>
     <row r="183" spans="1:14">
@@ -11310,28 +11607,28 @@
         <v>408</v>
       </c>
       <c r="G183" t="s">
-        <v>553</v>
+        <v>558</v>
       </c>
       <c r="H183" t="s">
-        <v>695</v>
+        <v>707</v>
       </c>
       <c r="I183" t="s">
-        <v>878</v>
+        <v>900</v>
       </c>
       <c r="J183" t="s">
-        <v>894</v>
+        <v>916</v>
       </c>
       <c r="K183" t="s">
-        <v>897</v>
+        <v>919</v>
       </c>
       <c r="L183" t="b">
         <v>0</v>
       </c>
       <c r="M183" t="s">
-        <v>900</v>
+        <v>921</v>
       </c>
       <c r="N183" t="s">
-        <v>1035</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="184" spans="1:14">
@@ -11351,31 +11648,31 @@
         <v>406</v>
       </c>
       <c r="F184" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="G184" t="s">
-        <v>554</v>
+        <v>559</v>
       </c>
       <c r="H184" t="s">
-        <v>696</v>
+        <v>708</v>
       </c>
       <c r="I184" t="s">
-        <v>879</v>
+        <v>901</v>
       </c>
       <c r="J184" t="s">
-        <v>894</v>
+        <v>916</v>
       </c>
       <c r="K184" t="s">
-        <v>897</v>
+        <v>919</v>
       </c>
       <c r="L184" t="b">
         <v>0</v>
       </c>
       <c r="M184" t="s">
-        <v>900</v>
+        <v>921</v>
       </c>
       <c r="N184" t="s">
-        <v>1036</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="185" spans="1:14">
@@ -11395,31 +11692,31 @@
         <v>406</v>
       </c>
       <c r="F185" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="G185" t="s">
-        <v>555</v>
+        <v>560</v>
       </c>
       <c r="H185" t="s">
-        <v>697</v>
+        <v>709</v>
       </c>
       <c r="I185" t="s">
-        <v>880</v>
+        <v>902</v>
       </c>
       <c r="J185" t="s">
-        <v>894</v>
+        <v>916</v>
       </c>
       <c r="K185" t="s">
-        <v>897</v>
+        <v>919</v>
       </c>
       <c r="L185" t="b">
         <v>0</v>
       </c>
       <c r="M185" t="s">
-        <v>900</v>
+        <v>921</v>
       </c>
       <c r="N185" t="s">
-        <v>1037</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="186" spans="1:14">
@@ -11439,31 +11736,31 @@
         <v>404</v>
       </c>
       <c r="F186" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="G186" t="s">
-        <v>524</v>
+        <v>529</v>
       </c>
       <c r="H186" t="s">
-        <v>654</v>
+        <v>666</v>
       </c>
       <c r="I186" t="s">
-        <v>881</v>
+        <v>903</v>
       </c>
       <c r="J186" t="s">
-        <v>894</v>
+        <v>916</v>
       </c>
       <c r="K186" t="s">
-        <v>897</v>
+        <v>919</v>
       </c>
       <c r="L186" t="b">
         <v>0</v>
       </c>
       <c r="M186" t="s">
-        <v>900</v>
+        <v>921</v>
       </c>
       <c r="N186" t="s">
-        <v>994</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="187" spans="1:14">
@@ -11486,28 +11783,28 @@
         <v>425</v>
       </c>
       <c r="G187" t="s">
-        <v>556</v>
+        <v>561</v>
       </c>
       <c r="H187" t="s">
-        <v>698</v>
+        <v>710</v>
       </c>
       <c r="I187" t="s">
-        <v>882</v>
+        <v>904</v>
       </c>
       <c r="J187" t="s">
-        <v>894</v>
+        <v>916</v>
       </c>
       <c r="K187" t="s">
-        <v>897</v>
+        <v>919</v>
       </c>
       <c r="L187" t="b">
         <v>0</v>
       </c>
       <c r="M187" t="s">
-        <v>900</v>
+        <v>921</v>
       </c>
       <c r="N187" t="s">
-        <v>1038</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="188" spans="1:14">
@@ -11527,31 +11824,31 @@
         <v>401</v>
       </c>
       <c r="F188" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="G188" t="s">
-        <v>557</v>
+        <v>562</v>
       </c>
       <c r="H188" t="s">
-        <v>699</v>
+        <v>711</v>
       </c>
       <c r="I188" t="s">
-        <v>883</v>
+        <v>905</v>
       </c>
       <c r="J188" t="s">
-        <v>895</v>
+        <v>917</v>
       </c>
       <c r="K188" t="s">
-        <v>898</v>
+        <v>920</v>
       </c>
       <c r="L188" t="b">
         <v>1</v>
       </c>
       <c r="M188" t="s">
-        <v>901</v>
+        <v>922</v>
       </c>
       <c r="N188" t="s">
-        <v>1039</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="189" spans="1:14">
@@ -11571,31 +11868,31 @@
         <v>401</v>
       </c>
       <c r="F189" t="s">
-        <v>454</v>
+        <v>439</v>
       </c>
       <c r="G189" t="s">
-        <v>558</v>
+        <v>563</v>
       </c>
       <c r="H189" t="s">
-        <v>700</v>
+        <v>712</v>
       </c>
       <c r="I189" t="s">
-        <v>884</v>
+        <v>906</v>
       </c>
       <c r="J189" t="s">
-        <v>894</v>
+        <v>916</v>
       </c>
       <c r="K189" t="s">
-        <v>897</v>
+        <v>919</v>
       </c>
       <c r="L189" t="b">
         <v>0</v>
       </c>
       <c r="M189" t="s">
-        <v>900</v>
+        <v>921</v>
       </c>
       <c r="N189" t="s">
-        <v>1040</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="190" spans="1:14">
@@ -11615,31 +11912,31 @@
         <v>401</v>
       </c>
       <c r="F190" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="G190" t="s">
-        <v>559</v>
+        <v>564</v>
       </c>
       <c r="H190" t="s">
-        <v>701</v>
+        <v>713</v>
       </c>
       <c r="I190" t="s">
-        <v>885</v>
+        <v>907</v>
       </c>
       <c r="J190" t="s">
-        <v>894</v>
+        <v>916</v>
       </c>
       <c r="K190" t="s">
-        <v>897</v>
+        <v>919</v>
       </c>
       <c r="L190" t="b">
         <v>0</v>
       </c>
       <c r="M190" t="s">
-        <v>900</v>
+        <v>921</v>
       </c>
       <c r="N190" t="s">
-        <v>1041</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="191" spans="1:14">
@@ -11662,28 +11959,28 @@
         <v>425</v>
       </c>
       <c r="G191" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="H191" t="s">
-        <v>609</v>
+        <v>613</v>
       </c>
       <c r="I191" t="s">
-        <v>886</v>
+        <v>908</v>
       </c>
       <c r="J191" t="s">
-        <v>894</v>
+        <v>916</v>
       </c>
       <c r="K191" t="s">
-        <v>897</v>
+        <v>919</v>
       </c>
       <c r="L191" t="b">
         <v>0</v>
       </c>
       <c r="M191" t="s">
-        <v>900</v>
+        <v>921</v>
       </c>
       <c r="N191" t="s">
-        <v>949</v>
+        <v>970</v>
       </c>
     </row>
     <row r="192" spans="1:14">
@@ -11706,28 +12003,28 @@
         <v>425</v>
       </c>
       <c r="G192" t="s">
-        <v>556</v>
+        <v>561</v>
       </c>
       <c r="H192" t="s">
-        <v>702</v>
+        <v>714</v>
       </c>
       <c r="I192" t="s">
-        <v>887</v>
+        <v>909</v>
       </c>
       <c r="J192" t="s">
-        <v>894</v>
+        <v>916</v>
       </c>
       <c r="K192" t="s">
-        <v>897</v>
+        <v>919</v>
       </c>
       <c r="L192" t="b">
         <v>0</v>
       </c>
       <c r="M192" t="s">
-        <v>900</v>
+        <v>921</v>
       </c>
       <c r="N192" t="s">
-        <v>1042</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="193" spans="1:14">
@@ -11750,28 +12047,28 @@
         <v>425</v>
       </c>
       <c r="G193" t="s">
-        <v>556</v>
+        <v>561</v>
       </c>
       <c r="H193" t="s">
-        <v>703</v>
+        <v>715</v>
       </c>
       <c r="I193" t="s">
-        <v>888</v>
+        <v>910</v>
       </c>
       <c r="J193" t="s">
-        <v>894</v>
+        <v>916</v>
       </c>
       <c r="K193" t="s">
-        <v>897</v>
+        <v>919</v>
       </c>
       <c r="L193" t="b">
         <v>0</v>
       </c>
       <c r="M193" t="s">
-        <v>900</v>
+        <v>921</v>
       </c>
       <c r="N193" t="s">
-        <v>1043</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="194" spans="1:14">
@@ -11794,28 +12091,28 @@
         <v>425</v>
       </c>
       <c r="G194" t="s">
-        <v>556</v>
+        <v>561</v>
       </c>
       <c r="H194" t="s">
-        <v>704</v>
+        <v>716</v>
       </c>
       <c r="I194" t="s">
-        <v>889</v>
+        <v>911</v>
       </c>
       <c r="J194" t="s">
-        <v>894</v>
+        <v>916</v>
       </c>
       <c r="K194" t="s">
-        <v>897</v>
+        <v>919</v>
       </c>
       <c r="L194" t="b">
         <v>0</v>
       </c>
       <c r="M194" t="s">
-        <v>900</v>
+        <v>921</v>
       </c>
       <c r="N194" t="s">
-        <v>1044</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="195" spans="1:14">
@@ -11838,28 +12135,28 @@
         <v>425</v>
       </c>
       <c r="G195" t="s">
-        <v>538</v>
+        <v>543</v>
       </c>
       <c r="H195" t="s">
-        <v>705</v>
+        <v>717</v>
       </c>
       <c r="I195" t="s">
-        <v>890</v>
+        <v>912</v>
       </c>
       <c r="J195" t="s">
-        <v>894</v>
+        <v>916</v>
       </c>
       <c r="K195" t="s">
-        <v>897</v>
+        <v>919</v>
       </c>
       <c r="L195" t="b">
         <v>0</v>
       </c>
       <c r="M195" t="s">
-        <v>900</v>
+        <v>921</v>
       </c>
       <c r="N195" t="s">
-        <v>1045</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="196" spans="1:14">
@@ -11879,31 +12176,31 @@
         <v>401</v>
       </c>
       <c r="F196" t="s">
-        <v>454</v>
+        <v>439</v>
       </c>
       <c r="G196" t="s">
-        <v>560</v>
+        <v>525</v>
       </c>
       <c r="H196" t="s">
-        <v>706</v>
+        <v>718</v>
       </c>
       <c r="I196" t="s">
-        <v>891</v>
+        <v>913</v>
       </c>
       <c r="J196" t="s">
-        <v>894</v>
+        <v>916</v>
       </c>
       <c r="K196" t="s">
-        <v>897</v>
+        <v>919</v>
       </c>
       <c r="L196" t="b">
         <v>0</v>
       </c>
       <c r="M196" t="s">
-        <v>900</v>
+        <v>921</v>
       </c>
       <c r="N196" t="s">
-        <v>1046</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="197" spans="1:14">
@@ -11926,28 +12223,28 @@
         <v>425</v>
       </c>
       <c r="G197" t="s">
-        <v>561</v>
+        <v>565</v>
       </c>
       <c r="H197" t="s">
-        <v>707</v>
+        <v>719</v>
       </c>
       <c r="I197" t="s">
-        <v>892</v>
+        <v>914</v>
       </c>
       <c r="J197" t="s">
-        <v>894</v>
+        <v>916</v>
       </c>
       <c r="K197" t="s">
-        <v>897</v>
+        <v>919</v>
       </c>
       <c r="L197" t="b">
         <v>0</v>
       </c>
       <c r="M197" t="s">
-        <v>900</v>
+        <v>921</v>
       </c>
       <c r="N197" t="s">
-        <v>1047</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="198" spans="1:14">
@@ -11970,28 +12267,28 @@
         <v>410</v>
       </c>
       <c r="G198" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="H198" t="s">
-        <v>568</v>
+        <v>572</v>
       </c>
       <c r="I198" t="s">
-        <v>893</v>
+        <v>915</v>
       </c>
       <c r="J198" t="s">
-        <v>895</v>
+        <v>917</v>
       </c>
       <c r="K198" t="s">
-        <v>898</v>
+        <v>920</v>
       </c>
       <c r="L198" t="b">
         <v>1</v>
       </c>
       <c r="M198" t="s">
-        <v>901</v>
+        <v>922</v>
       </c>
       <c r="N198" t="s">
-        <v>908</v>
+        <v>929</v>
       </c>
     </row>
   </sheetData>
